--- a/data/raw/expert_scores.xlsx
+++ b/data/raw/expert_scores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29819"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universiteittwente-my.sharepoint.com/personal/m_sikora_utwente_nl/Documents/Desktop/PhD_Stress-In-Action/01_Database/Dashboard/relational/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universiteittwente.sharepoint.com/sites/Stress-in-Action/Gedeelde documenten/General/_Relational - SiA-WD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="218" documentId="8_{B8FE1228-C429-432C-94A2-C1F64831892C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCC25A23-20B7-4295-A2AA-443983374659}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76F443B9-2CFB-4DCD-9AF3-787198A5CAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12960" yWindow="-18120" windowWidth="29040" windowHeight="17520" xr2:uid="{2C9CAB11-EC45-49EE-BE20-1107D0FD28A6}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{2C9CAB11-EC45-49EE-BE20-1107D0FD28A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="58">
   <si>
     <t>device_id</t>
   </si>
@@ -121,12 +121,102 @@
   <si>
     <t>015_sia_wd_app</t>
   </si>
+  <si>
+    <t>016_sia_wd_app</t>
+  </si>
+  <si>
+    <t>017_sia_wd_bio</t>
+  </si>
+  <si>
+    <t>018_sia_wd_now</t>
+  </si>
+  <si>
+    <t>019_sia_wd_goo</t>
+  </si>
+  <si>
+    <t>020_sia_wd_goo</t>
+  </si>
+  <si>
+    <t>021_sia_wd_cor</t>
+  </si>
+  <si>
+    <t>022_sia_wd_cor</t>
+  </si>
+  <si>
+    <t>023_sia_wd_bio</t>
+  </si>
+  <si>
+    <t>024_sia_wd_fit</t>
+  </si>
+  <si>
+    <t>025_sia_wd_fit</t>
+  </si>
+  <si>
+    <t>026_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>027_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>028_sia_wd_who</t>
+  </si>
+  <si>
+    <t>029_sia_wd_who</t>
+  </si>
+  <si>
+    <t>030_sia_wd_cir</t>
+  </si>
+  <si>
+    <t>031_sia_wd_mov</t>
+  </si>
+  <si>
+    <t>032_sia_wd_wit</t>
+  </si>
+  <si>
+    <t>033_sia_wd_wit</t>
+  </si>
+  <si>
+    <t>034_sia_wd_spa</t>
+  </si>
+  <si>
+    <t>035_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>036_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>037_sia_wd_gar</t>
+  </si>
+  <si>
+    <t>038_sia_wd_sky</t>
+  </si>
+  <si>
+    <t>039_sia_wd_ama</t>
+  </si>
+  <si>
+    <t>040_sia_wd_bio</t>
+  </si>
+  <si>
+    <t>041_sia_wd_car</t>
+  </si>
+  <si>
+    <t>042_sia_wd_sam</t>
+  </si>
+  <si>
+    <t>043_sia_wd_goo</t>
+  </si>
+  <si>
+    <t>044_sia_wd_adi</t>
+  </si>
+  <si>
+    <t>045_sia_wd_med</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +244,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -163,7 +259,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -189,11 +285,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -212,12 +317,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -552,8 +659,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52AC09CD-A4FA-4E91-BDBC-BF7CF9B4D46E}">
-  <dimension ref="A1:G137"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:G369"/>
+  <sheetFormatPr defaultRowHeight="14.65"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
@@ -812,7 +919,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15">
+    <row r="18" spans="1:4">
       <c r="A18" s="10" t="s">
         <v>15</v>
       </c>
@@ -826,7 +933,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15">
+    <row r="19" spans="1:4">
       <c r="A19" s="10" t="s">
         <v>15</v>
       </c>
@@ -840,7 +947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15">
+    <row r="20" spans="1:4">
       <c r="A20" s="10" t="s">
         <v>15</v>
       </c>
@@ -854,7 +961,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15">
+    <row r="21" spans="1:4">
       <c r="A21" s="10" t="s">
         <v>15</v>
       </c>
@@ -868,7 +975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15">
+    <row r="22" spans="1:4">
       <c r="A22" s="10" t="s">
         <v>15</v>
       </c>
@@ -882,7 +989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15">
+    <row r="23" spans="1:4">
       <c r="A23" s="10" t="s">
         <v>15</v>
       </c>
@@ -896,7 +1003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15">
+    <row r="24" spans="1:4">
       <c r="A24" s="10" t="s">
         <v>15</v>
       </c>
@@ -910,8 +1017,8 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A25" s="13" t="s">
+    <row r="25" spans="1:4" s="8" customFormat="1">
+      <c r="A25" s="11" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -924,21 +1031,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15">
+    <row r="26" spans="1:4">
       <c r="A26" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="11" t="s">
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15">
+    <row r="27" spans="1:4">
       <c r="A27" s="10" t="s">
         <v>16</v>
       </c>
@@ -952,7 +1059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15">
+    <row r="28" spans="1:4">
       <c r="A28" s="10" t="s">
         <v>16</v>
       </c>
@@ -966,7 +1073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15">
+    <row r="29" spans="1:4">
       <c r="A29" s="10" t="s">
         <v>16</v>
       </c>
@@ -980,7 +1087,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15">
+    <row r="30" spans="1:4">
       <c r="A30" s="10" t="s">
         <v>16</v>
       </c>
@@ -994,7 +1101,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15">
+    <row r="31" spans="1:4">
       <c r="A31" s="10" t="s">
         <v>16</v>
       </c>
@@ -1008,7 +1115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15">
+    <row r="32" spans="1:4">
       <c r="A32" s="10" t="s">
         <v>16</v>
       </c>
@@ -1022,8 +1129,8 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="33" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A33" s="13" t="s">
+    <row r="33" spans="1:4" s="8" customFormat="1">
+      <c r="A33" s="11" t="s">
         <v>16</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -1036,21 +1143,21 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15">
+    <row r="34" spans="1:4">
       <c r="A34" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="11" t="s">
+      <c r="B34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15">
+    <row r="35" spans="1:4">
       <c r="A35" s="10" t="s">
         <v>17</v>
       </c>
@@ -1064,7 +1171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15">
+    <row r="36" spans="1:4">
       <c r="A36" s="10" t="s">
         <v>17</v>
       </c>
@@ -1078,7 +1185,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15">
+    <row r="37" spans="1:4">
       <c r="A37" s="10" t="s">
         <v>17</v>
       </c>
@@ -1092,7 +1199,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15">
+    <row r="38" spans="1:4">
       <c r="A38" s="10" t="s">
         <v>17</v>
       </c>
@@ -1106,7 +1213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15">
+    <row r="39" spans="1:4">
       <c r="A39" s="10" t="s">
         <v>17</v>
       </c>
@@ -1120,7 +1227,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15">
+    <row r="40" spans="1:4">
       <c r="A40" s="10" t="s">
         <v>17</v>
       </c>
@@ -1134,8 +1241,8 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="41" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A41" s="13" t="s">
+    <row r="41" spans="1:4" s="8" customFormat="1">
+      <c r="A41" s="11" t="s">
         <v>17</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -1148,21 +1255,21 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15">
+    <row r="42" spans="1:4">
       <c r="A42" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B42" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="11" t="s">
+      <c r="B42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15">
+    <row r="43" spans="1:4">
       <c r="A43" s="10" t="s">
         <v>18</v>
       </c>
@@ -1176,7 +1283,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15">
+    <row r="44" spans="1:4">
       <c r="A44" s="10" t="s">
         <v>18</v>
       </c>
@@ -1190,7 +1297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15">
+    <row r="45" spans="1:4">
       <c r="A45" s="10" t="s">
         <v>18</v>
       </c>
@@ -1204,7 +1311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15">
+    <row r="46" spans="1:4">
       <c r="A46" s="10" t="s">
         <v>18</v>
       </c>
@@ -1218,7 +1325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15">
+    <row r="47" spans="1:4">
       <c r="A47" s="10" t="s">
         <v>18</v>
       </c>
@@ -1232,7 +1339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15">
+    <row r="48" spans="1:4">
       <c r="A48" s="10" t="s">
         <v>18</v>
       </c>
@@ -1246,8 +1353,8 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="49" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A49" s="13" t="s">
+    <row r="49" spans="1:4" s="8" customFormat="1">
+      <c r="A49" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -1260,21 +1367,21 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15">
+    <row r="50" spans="1:4">
       <c r="A50" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B50" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C50" s="11" t="s">
+      <c r="B50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15">
+    <row r="51" spans="1:4">
       <c r="A51" s="10" t="s">
         <v>19</v>
       </c>
@@ -1288,7 +1395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15">
+    <row r="52" spans="1:4">
       <c r="A52" s="10" t="s">
         <v>19</v>
       </c>
@@ -1302,7 +1409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15">
+    <row r="53" spans="1:4">
       <c r="A53" s="10" t="s">
         <v>19</v>
       </c>
@@ -1316,7 +1423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15">
+    <row r="54" spans="1:4">
       <c r="A54" s="10" t="s">
         <v>19</v>
       </c>
@@ -1330,7 +1437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15">
+    <row r="55" spans="1:4">
       <c r="A55" s="10" t="s">
         <v>19</v>
       </c>
@@ -1344,7 +1451,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15">
+    <row r="56" spans="1:4">
       <c r="A56" s="10" t="s">
         <v>19</v>
       </c>
@@ -1358,8 +1465,8 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="57" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A57" s="13" t="s">
+    <row r="57" spans="1:4" s="8" customFormat="1">
+      <c r="A57" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B57" s="8" t="s">
@@ -1372,21 +1479,21 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15">
+    <row r="58" spans="1:4">
       <c r="A58" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B58" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C58" s="11" t="s">
+      <c r="B58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15">
+    <row r="59" spans="1:4">
       <c r="A59" s="10" t="s">
         <v>20</v>
       </c>
@@ -1400,7 +1507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15">
+    <row r="60" spans="1:4">
       <c r="A60" s="10" t="s">
         <v>20</v>
       </c>
@@ -1414,7 +1521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="15">
+    <row r="61" spans="1:4">
       <c r="A61" s="10" t="s">
         <v>20</v>
       </c>
@@ -1428,7 +1535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="15">
+    <row r="62" spans="1:4">
       <c r="A62" s="10" t="s">
         <v>20</v>
       </c>
@@ -1442,7 +1549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="15">
+    <row r="63" spans="1:4">
       <c r="A63" s="10" t="s">
         <v>20</v>
       </c>
@@ -1456,7 +1563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="15">
+    <row r="64" spans="1:4">
       <c r="A64" s="10" t="s">
         <v>20</v>
       </c>
@@ -1470,8 +1577,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A65" s="13" t="s">
+    <row r="65" spans="1:4" s="8" customFormat="1">
+      <c r="A65" s="11" t="s">
         <v>20</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -1484,21 +1591,21 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="15">
+    <row r="66" spans="1:4">
       <c r="A66" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B66" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C66" s="11" t="s">
+      <c r="B66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
         <v>6</v>
       </c>
       <c r="D66" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15">
+    <row r="67" spans="1:4">
       <c r="A67" s="10" t="s">
         <v>21</v>
       </c>
@@ -1512,7 +1619,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="15">
+    <row r="68" spans="1:4">
       <c r="A68" s="10" t="s">
         <v>21</v>
       </c>
@@ -1526,7 +1633,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15">
+    <row r="69" spans="1:4">
       <c r="A69" s="10" t="s">
         <v>21</v>
       </c>
@@ -1540,7 +1647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15">
+    <row r="70" spans="1:4">
       <c r="A70" s="10" t="s">
         <v>21</v>
       </c>
@@ -1554,7 +1661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15">
+    <row r="71" spans="1:4">
       <c r="A71" s="10" t="s">
         <v>21</v>
       </c>
@@ -1568,7 +1675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15">
+    <row r="72" spans="1:4">
       <c r="A72" s="10" t="s">
         <v>21</v>
       </c>
@@ -1582,8 +1689,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A73" s="13" t="s">
+    <row r="73" spans="1:4" s="8" customFormat="1">
+      <c r="A73" s="11" t="s">
         <v>21</v>
       </c>
       <c r="B73" s="8" t="s">
@@ -1596,21 +1703,21 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="15">
+    <row r="74" spans="1:4">
       <c r="A74" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B74" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C74" s="11" t="s">
+      <c r="B74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" t="s">
         <v>6</v>
       </c>
       <c r="D74" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="15">
+    <row r="75" spans="1:4">
       <c r="A75" s="10" t="s">
         <v>22</v>
       </c>
@@ -1624,7 +1731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15">
+    <row r="76" spans="1:4">
       <c r="A76" s="10" t="s">
         <v>22</v>
       </c>
@@ -1638,7 +1745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15">
+    <row r="77" spans="1:4">
       <c r="A77" s="10" t="s">
         <v>22</v>
       </c>
@@ -1652,7 +1759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15">
+    <row r="78" spans="1:4">
       <c r="A78" s="10" t="s">
         <v>22</v>
       </c>
@@ -1666,7 +1773,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="15">
+    <row r="79" spans="1:4">
       <c r="A79" s="10" t="s">
         <v>22</v>
       </c>
@@ -1680,7 +1787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="15">
+    <row r="80" spans="1:4">
       <c r="A80" s="10" t="s">
         <v>22</v>
       </c>
@@ -1694,8 +1801,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A81" s="13" t="s">
+    <row r="81" spans="1:4" s="8" customFormat="1">
+      <c r="A81" s="11" t="s">
         <v>22</v>
       </c>
       <c r="B81" s="8" t="s">
@@ -1708,21 +1815,21 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15">
+    <row r="82" spans="1:4">
       <c r="A82" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B82" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C82" s="11" t="s">
+      <c r="B82" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" t="s">
         <v>6</v>
       </c>
       <c r="D82" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="15">
+    <row r="83" spans="1:4">
       <c r="A83" s="10" t="s">
         <v>23</v>
       </c>
@@ -1736,7 +1843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="15">
+    <row r="84" spans="1:4">
       <c r="A84" s="10" t="s">
         <v>23</v>
       </c>
@@ -1750,7 +1857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15">
+    <row r="85" spans="1:4">
       <c r="A85" s="10" t="s">
         <v>23</v>
       </c>
@@ -1764,7 +1871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15">
+    <row r="86" spans="1:4">
       <c r="A86" s="10" t="s">
         <v>23</v>
       </c>
@@ -1778,7 +1885,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15">
+    <row r="87" spans="1:4">
       <c r="A87" s="10" t="s">
         <v>23</v>
       </c>
@@ -1792,7 +1899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="15">
+    <row r="88" spans="1:4">
       <c r="A88" s="10" t="s">
         <v>23</v>
       </c>
@@ -1806,8 +1913,8 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="89" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A89" s="13" t="s">
+    <row r="89" spans="1:4" s="8" customFormat="1">
+      <c r="A89" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B89" s="8" t="s">
@@ -1820,21 +1927,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="15">
+    <row r="90" spans="1:4">
       <c r="A90" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B90" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" s="11" t="s">
+      <c r="B90" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" t="s">
         <v>6</v>
       </c>
       <c r="D90" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15">
+    <row r="91" spans="1:4">
       <c r="A91" s="10" t="s">
         <v>24</v>
       </c>
@@ -1848,7 +1955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15">
+    <row r="92" spans="1:4">
       <c r="A92" s="10" t="s">
         <v>24</v>
       </c>
@@ -1862,7 +1969,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="15">
+    <row r="93" spans="1:4">
       <c r="A93" s="10" t="s">
         <v>24</v>
       </c>
@@ -1876,7 +1983,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="15">
+    <row r="94" spans="1:4">
       <c r="A94" s="10" t="s">
         <v>24</v>
       </c>
@@ -1890,7 +1997,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="15">
+    <row r="95" spans="1:4">
       <c r="A95" s="10" t="s">
         <v>24</v>
       </c>
@@ -1904,7 +2011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="15">
+    <row r="96" spans="1:4">
       <c r="A96" s="10" t="s">
         <v>24</v>
       </c>
@@ -1918,8 +2025,8 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="97" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A97" s="13" t="s">
+    <row r="97" spans="1:4" s="8" customFormat="1">
+      <c r="A97" s="11" t="s">
         <v>24</v>
       </c>
       <c r="B97" s="8" t="s">
@@ -1932,21 +2039,21 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="15">
+    <row r="98" spans="1:4">
       <c r="A98" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B98" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C98" s="11" t="s">
+      <c r="B98" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" t="s">
         <v>6</v>
       </c>
       <c r="D98" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="15">
+    <row r="99" spans="1:4">
       <c r="A99" s="10" t="s">
         <v>25</v>
       </c>
@@ -1960,7 +2067,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="15">
+    <row r="100" spans="1:4">
       <c r="A100" s="10" t="s">
         <v>25</v>
       </c>
@@ -1974,7 +2081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="15">
+    <row r="101" spans="1:4">
       <c r="A101" s="10" t="s">
         <v>25</v>
       </c>
@@ -1988,7 +2095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="15">
+    <row r="102" spans="1:4">
       <c r="A102" s="10" t="s">
         <v>25</v>
       </c>
@@ -2002,7 +2109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="15">
+    <row r="103" spans="1:4">
       <c r="A103" s="10" t="s">
         <v>25</v>
       </c>
@@ -2016,7 +2123,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="15">
+    <row r="104" spans="1:4">
       <c r="A104" s="10" t="s">
         <v>25</v>
       </c>
@@ -2030,8 +2137,8 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="105" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A105" s="13" t="s">
+    <row r="105" spans="1:4" s="8" customFormat="1">
+      <c r="A105" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B105" s="8" t="s">
@@ -2044,21 +2151,21 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="15">
+    <row r="106" spans="1:4">
       <c r="A106" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B106" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C106" s="11" t="s">
+      <c r="B106" t="s">
+        <v>5</v>
+      </c>
+      <c r="C106" t="s">
         <v>6</v>
       </c>
       <c r="D106" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="15">
+    <row r="107" spans="1:4">
       <c r="A107" s="10" t="s">
         <v>26</v>
       </c>
@@ -2072,7 +2179,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="15">
+    <row r="108" spans="1:4">
       <c r="A108" s="10" t="s">
         <v>26</v>
       </c>
@@ -2086,7 +2193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="15">
+    <row r="109" spans="1:4">
       <c r="A109" s="10" t="s">
         <v>26</v>
       </c>
@@ -2100,7 +2207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="15">
+    <row r="110" spans="1:4">
       <c r="A110" s="10" t="s">
         <v>26</v>
       </c>
@@ -2114,7 +2221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="15">
+    <row r="111" spans="1:4">
       <c r="A111" s="10" t="s">
         <v>26</v>
       </c>
@@ -2128,7 +2235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="15">
+    <row r="112" spans="1:4">
       <c r="A112" s="10" t="s">
         <v>26</v>
       </c>
@@ -2142,8 +2249,8 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A113" s="13" t="s">
+    <row r="113" spans="1:4" s="8" customFormat="1">
+      <c r="A113" s="11" t="s">
         <v>26</v>
       </c>
       <c r="B113" s="8" t="s">
@@ -2156,21 +2263,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="15">
+    <row r="114" spans="1:4">
       <c r="A114" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B114" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C114" s="11" t="s">
+      <c r="B114" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" t="s">
         <v>6</v>
       </c>
       <c r="D114" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="15">
+    <row r="115" spans="1:4">
       <c r="A115" s="10" t="s">
         <v>27</v>
       </c>
@@ -2184,7 +2291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="15">
+    <row r="116" spans="1:4">
       <c r="A116" s="10" t="s">
         <v>27</v>
       </c>
@@ -2198,7 +2305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="15">
+    <row r="117" spans="1:4">
       <c r="A117" s="10" t="s">
         <v>27</v>
       </c>
@@ -2212,7 +2319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="15">
+    <row r="118" spans="1:4">
       <c r="A118" s="10" t="s">
         <v>27</v>
       </c>
@@ -2226,7 +2333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="15">
+    <row r="119" spans="1:4">
       <c r="A119" s="10" t="s">
         <v>27</v>
       </c>
@@ -2240,7 +2347,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="15">
+    <row r="120" spans="1:4">
       <c r="A120" s="10" t="s">
         <v>27</v>
       </c>
@@ -2254,8 +2361,8 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="121" spans="1:4" s="8" customFormat="1" ht="15">
-      <c r="A121" s="13" t="s">
+    <row r="121" spans="1:4" s="8" customFormat="1">
+      <c r="A121" s="11" t="s">
         <v>27</v>
       </c>
       <c r="B121" s="8" t="s">
@@ -2268,102 +2375,3374 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
-      <c r="A122" s="11"/>
-      <c r="B122" s="11"/>
-      <c r="C122" s="11"/>
-      <c r="D122" s="12"/>
+    <row r="122" spans="1:4" ht="15">
+      <c r="A122" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C122" t="s">
+        <v>6</v>
+      </c>
+      <c r="D122" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="123" spans="1:4">
-      <c r="A123" s="11"/>
-      <c r="B123" s="11"/>
-      <c r="C123" s="11"/>
-      <c r="D123" s="12"/>
+      <c r="A123" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B123" t="s">
+        <v>7</v>
+      </c>
+      <c r="C123" t="s">
+        <v>6</v>
+      </c>
+      <c r="D123" s="6">
+        <v>6</v>
+      </c>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124" s="11"/>
-      <c r="B124" s="11"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="12"/>
+      <c r="A124" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B124" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125" s="11"/>
-      <c r="B125" s="11"/>
-      <c r="C125" s="11"/>
-      <c r="D125" s="12"/>
+      <c r="A125" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B125" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="6">
+        <v>6</v>
+      </c>
     </row>
     <row r="126" spans="1:4">
-      <c r="A126" s="11"/>
-      <c r="B126" s="11"/>
-      <c r="C126" s="11"/>
-      <c r="D126" s="12"/>
+      <c r="A126" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B126" t="s">
+        <v>5</v>
+      </c>
+      <c r="C126" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="127" spans="1:4">
-      <c r="A127" s="11"/>
-      <c r="B127" s="11"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="12"/>
+      <c r="A127" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B127" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="6">
+        <v>6</v>
+      </c>
     </row>
     <row r="128" spans="1:4">
-      <c r="A128" s="11"/>
-      <c r="B128" s="11"/>
-      <c r="C128" s="11"/>
-      <c r="D128" s="12"/>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="A129" s="11"/>
-      <c r="B129" s="11"/>
-      <c r="C129" s="11"/>
-      <c r="D129" s="12"/>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130" s="11"/>
-      <c r="B130" s="11"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="12"/>
+      <c r="A128" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B128" t="s">
+        <v>5</v>
+      </c>
+      <c r="C128" t="s">
+        <v>10</v>
+      </c>
+      <c r="D128" s="6">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" s="12" customFormat="1">
+      <c r="A129" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="15">
+      <c r="A130" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C130" t="s">
+        <v>6</v>
+      </c>
+      <c r="D130" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="131" spans="1:4">
-      <c r="A131" s="11"/>
-      <c r="B131" s="11"/>
-      <c r="C131" s="11"/>
-      <c r="D131" s="12"/>
+      <c r="A131" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B131" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" t="s">
+        <v>6</v>
+      </c>
+      <c r="D131" s="6">
+        <v>6</v>
+      </c>
     </row>
     <row r="132" spans="1:4">
-      <c r="A132" s="11"/>
-      <c r="B132" s="11"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="12"/>
+      <c r="A132" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B132" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132" t="s">
+        <v>8</v>
+      </c>
+      <c r="D132" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="133" spans="1:4">
-      <c r="A133" s="11"/>
-      <c r="B133" s="11"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="12"/>
+      <c r="A133" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B133" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" t="s">
+        <v>8</v>
+      </c>
+      <c r="D133" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="134" spans="1:4">
-      <c r="A134" s="11"/>
-      <c r="B134" s="11"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="12"/>
+      <c r="A134" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B134" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="6">
+        <v>5</v>
+      </c>
     </row>
     <row r="135" spans="1:4">
-      <c r="A135" s="11"/>
-      <c r="B135" s="11"/>
-      <c r="C135" s="11"/>
-      <c r="D135" s="12"/>
+      <c r="A135" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B135" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="136" spans="1:4">
-      <c r="A136" s="11"/>
-      <c r="B136" s="11"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="12"/>
-    </row>
-    <row r="137" spans="1:4">
-      <c r="A137" s="11"/>
-      <c r="B137" s="11"/>
-      <c r="C137" s="11"/>
-      <c r="D137" s="12"/>
-    </row>
+      <c r="A136" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B136" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" t="s">
+        <v>10</v>
+      </c>
+      <c r="D136" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" s="12" customFormat="1">
+      <c r="A137" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" t="s">
+        <v>10</v>
+      </c>
+      <c r="D137" s="13">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15">
+      <c r="A138" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C138" t="s">
+        <v>6</v>
+      </c>
+      <c r="D138" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B139" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" t="s">
+        <v>6</v>
+      </c>
+      <c r="D139" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B140" t="s">
+        <v>5</v>
+      </c>
+      <c r="C140" t="s">
+        <v>8</v>
+      </c>
+      <c r="D140" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B141" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141" t="s">
+        <v>8</v>
+      </c>
+      <c r="D141" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B142" t="s">
+        <v>5</v>
+      </c>
+      <c r="C142" t="s">
+        <v>9</v>
+      </c>
+      <c r="D142" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B143" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" t="s">
+        <v>9</v>
+      </c>
+      <c r="D143" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B144" t="s">
+        <v>5</v>
+      </c>
+      <c r="C144" t="s">
+        <v>10</v>
+      </c>
+      <c r="D144" s="6">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" s="12" customFormat="1">
+      <c r="A145" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B145" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C145" t="s">
+        <v>10</v>
+      </c>
+      <c r="D145" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="15">
+      <c r="A146" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C146" t="s">
+        <v>6</v>
+      </c>
+      <c r="D146" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B147" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" t="s">
+        <v>6</v>
+      </c>
+      <c r="D147" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B148" t="s">
+        <v>5</v>
+      </c>
+      <c r="C148" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B149" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" t="s">
+        <v>8</v>
+      </c>
+      <c r="D149" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B150" t="s">
+        <v>5</v>
+      </c>
+      <c r="C150" t="s">
+        <v>9</v>
+      </c>
+      <c r="D150" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B151" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151" t="s">
+        <v>9</v>
+      </c>
+      <c r="D151" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B152" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152" t="s">
+        <v>10</v>
+      </c>
+      <c r="D152" s="6">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" s="12" customFormat="1">
+      <c r="A153" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B153" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" t="s">
+        <v>10</v>
+      </c>
+      <c r="D153" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15">
+      <c r="A154" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C154" t="s">
+        <v>6</v>
+      </c>
+      <c r="D154" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B155" t="s">
+        <v>7</v>
+      </c>
+      <c r="C155" t="s">
+        <v>6</v>
+      </c>
+      <c r="D155" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B156" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B157" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B158" t="s">
+        <v>5</v>
+      </c>
+      <c r="C158" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B159" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" t="s">
+        <v>9</v>
+      </c>
+      <c r="D159" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B160" t="s">
+        <v>5</v>
+      </c>
+      <c r="C160" t="s">
+        <v>10</v>
+      </c>
+      <c r="D160" s="6">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" s="12" customFormat="1">
+      <c r="A161" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B161" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" t="s">
+        <v>10</v>
+      </c>
+      <c r="D161" s="13">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="15">
+      <c r="A162" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C162" t="s">
+        <v>6</v>
+      </c>
+      <c r="D162" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B163" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" t="s">
+        <v>6</v>
+      </c>
+      <c r="D163" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B164" t="s">
+        <v>5</v>
+      </c>
+      <c r="C164" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B165" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B166" t="s">
+        <v>5</v>
+      </c>
+      <c r="C166" t="s">
+        <v>9</v>
+      </c>
+      <c r="D166" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B167" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B168" t="s">
+        <v>5</v>
+      </c>
+      <c r="C168" t="s">
+        <v>10</v>
+      </c>
+      <c r="D168" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" s="12" customFormat="1">
+      <c r="A169" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" t="s">
+        <v>10</v>
+      </c>
+      <c r="D169" s="13">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="15">
+      <c r="A170" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C170" t="s">
+        <v>6</v>
+      </c>
+      <c r="D170" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B171" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" t="s">
+        <v>6</v>
+      </c>
+      <c r="D171" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B172" t="s">
+        <v>5</v>
+      </c>
+      <c r="C172" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B173" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" t="s">
+        <v>8</v>
+      </c>
+      <c r="D173" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B174" t="s">
+        <v>5</v>
+      </c>
+      <c r="C174" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B175" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" t="s">
+        <v>9</v>
+      </c>
+      <c r="D175" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B176" t="s">
+        <v>5</v>
+      </c>
+      <c r="C176" t="s">
+        <v>10</v>
+      </c>
+      <c r="D176" s="6">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" s="12" customFormat="1">
+      <c r="A177" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177" t="s">
+        <v>10</v>
+      </c>
+      <c r="D177" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="15">
+      <c r="A178" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C178" t="s">
+        <v>6</v>
+      </c>
+      <c r="D178" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B179" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179" t="s">
+        <v>6</v>
+      </c>
+      <c r="D179" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B180" t="s">
+        <v>5</v>
+      </c>
+      <c r="C180" t="s">
+        <v>8</v>
+      </c>
+      <c r="D180" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B181" t="s">
+        <v>7</v>
+      </c>
+      <c r="C181" t="s">
+        <v>8</v>
+      </c>
+      <c r="D181" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B182" t="s">
+        <v>5</v>
+      </c>
+      <c r="C182" t="s">
+        <v>9</v>
+      </c>
+      <c r="D182" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B183" t="s">
+        <v>7</v>
+      </c>
+      <c r="C183" t="s">
+        <v>9</v>
+      </c>
+      <c r="D183" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B184" t="s">
+        <v>5</v>
+      </c>
+      <c r="C184" t="s">
+        <v>10</v>
+      </c>
+      <c r="D184" s="6">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" s="12" customFormat="1">
+      <c r="A185" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B185" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C185" t="s">
+        <v>10</v>
+      </c>
+      <c r="D185" s="13">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="15">
+      <c r="A186" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C186" t="s">
+        <v>6</v>
+      </c>
+      <c r="D186" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="15">
+      <c r="A187" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B187" t="s">
+        <v>7</v>
+      </c>
+      <c r="C187" t="s">
+        <v>6</v>
+      </c>
+      <c r="D187" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="15">
+      <c r="A188" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B188" t="s">
+        <v>5</v>
+      </c>
+      <c r="C188" t="s">
+        <v>8</v>
+      </c>
+      <c r="D188" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="15">
+      <c r="A189" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B189" t="s">
+        <v>7</v>
+      </c>
+      <c r="C189" t="s">
+        <v>8</v>
+      </c>
+      <c r="D189" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="15">
+      <c r="A190" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B190" t="s">
+        <v>5</v>
+      </c>
+      <c r="C190" t="s">
+        <v>9</v>
+      </c>
+      <c r="D190" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15">
+      <c r="A191" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B191" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191" t="s">
+        <v>9</v>
+      </c>
+      <c r="D191" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="15">
+      <c r="A192" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B192" t="s">
+        <v>5</v>
+      </c>
+      <c r="C192" t="s">
+        <v>10</v>
+      </c>
+      <c r="D192" s="6">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" s="12" customFormat="1" ht="15">
+      <c r="A193" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B193" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C193" t="s">
+        <v>10</v>
+      </c>
+      <c r="D193" s="13">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="15">
+      <c r="A194" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C194" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="15">
+      <c r="A195" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B195" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195" t="s">
+        <v>6</v>
+      </c>
+      <c r="D195" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="15">
+      <c r="A196" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B196" t="s">
+        <v>5</v>
+      </c>
+      <c r="C196" t="s">
+        <v>8</v>
+      </c>
+      <c r="D196" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="15">
+      <c r="A197" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B197" t="s">
+        <v>7</v>
+      </c>
+      <c r="C197" t="s">
+        <v>8</v>
+      </c>
+      <c r="D197" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="15">
+      <c r="A198" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B198" t="s">
+        <v>5</v>
+      </c>
+      <c r="C198" t="s">
+        <v>9</v>
+      </c>
+      <c r="D198" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="15">
+      <c r="A199" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B199" t="s">
+        <v>7</v>
+      </c>
+      <c r="C199" t="s">
+        <v>9</v>
+      </c>
+      <c r="D199" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="15">
+      <c r="A200" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B200" t="s">
+        <v>5</v>
+      </c>
+      <c r="C200" t="s">
+        <v>10</v>
+      </c>
+      <c r="D200" s="6">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" s="12" customFormat="1" ht="15">
+      <c r="A201" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B201" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C201" t="s">
+        <v>10</v>
+      </c>
+      <c r="D201" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="15">
+      <c r="A202" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C202" t="s">
+        <v>6</v>
+      </c>
+      <c r="D202" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B203" t="s">
+        <v>7</v>
+      </c>
+      <c r="C203" t="s">
+        <v>6</v>
+      </c>
+      <c r="D203" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B204" t="s">
+        <v>5</v>
+      </c>
+      <c r="C204" t="s">
+        <v>8</v>
+      </c>
+      <c r="D204" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B205" t="s">
+        <v>7</v>
+      </c>
+      <c r="C205" t="s">
+        <v>8</v>
+      </c>
+      <c r="D205" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B206" t="s">
+        <v>5</v>
+      </c>
+      <c r="C206" t="s">
+        <v>9</v>
+      </c>
+      <c r="D206" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B207" t="s">
+        <v>7</v>
+      </c>
+      <c r="C207" t="s">
+        <v>9</v>
+      </c>
+      <c r="D207" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B208" t="s">
+        <v>5</v>
+      </c>
+      <c r="C208" t="s">
+        <v>10</v>
+      </c>
+      <c r="D208" s="6">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" s="12" customFormat="1">
+      <c r="A209" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B209" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C209" t="s">
+        <v>10</v>
+      </c>
+      <c r="D209" s="13">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="15">
+      <c r="A210" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C210" t="s">
+        <v>6</v>
+      </c>
+      <c r="D210" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B211" t="s">
+        <v>7</v>
+      </c>
+      <c r="C211" t="s">
+        <v>6</v>
+      </c>
+      <c r="D211" s="6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B212" t="s">
+        <v>5</v>
+      </c>
+      <c r="C212" t="s">
+        <v>8</v>
+      </c>
+      <c r="D212" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B213" t="s">
+        <v>7</v>
+      </c>
+      <c r="C213" t="s">
+        <v>8</v>
+      </c>
+      <c r="D213" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B214" t="s">
+        <v>5</v>
+      </c>
+      <c r="C214" t="s">
+        <v>9</v>
+      </c>
+      <c r="D214" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B215" t="s">
+        <v>7</v>
+      </c>
+      <c r="C215" t="s">
+        <v>9</v>
+      </c>
+      <c r="D215" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B216" t="s">
+        <v>5</v>
+      </c>
+      <c r="C216" t="s">
+        <v>10</v>
+      </c>
+      <c r="D216" s="6">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" s="12" customFormat="1">
+      <c r="A217" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B217" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C217" t="s">
+        <v>10</v>
+      </c>
+      <c r="D217" s="13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="15">
+      <c r="A218" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C218" t="s">
+        <v>6</v>
+      </c>
+      <c r="D218" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="15">
+      <c r="A219" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B219" t="s">
+        <v>7</v>
+      </c>
+      <c r="C219" t="s">
+        <v>6</v>
+      </c>
+      <c r="D219" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="15">
+      <c r="A220" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B220" t="s">
+        <v>5</v>
+      </c>
+      <c r="C220" t="s">
+        <v>8</v>
+      </c>
+      <c r="D220" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="15">
+      <c r="A221" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B221" t="s">
+        <v>7</v>
+      </c>
+      <c r="C221" t="s">
+        <v>8</v>
+      </c>
+      <c r="D221" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="15">
+      <c r="A222" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B222" t="s">
+        <v>5</v>
+      </c>
+      <c r="C222" t="s">
+        <v>9</v>
+      </c>
+      <c r="D222" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" ht="15">
+      <c r="A223" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B223" t="s">
+        <v>7</v>
+      </c>
+      <c r="C223" t="s">
+        <v>9</v>
+      </c>
+      <c r="D223" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" ht="15">
+      <c r="A224" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B224" t="s">
+        <v>5</v>
+      </c>
+      <c r="C224" t="s">
+        <v>10</v>
+      </c>
+      <c r="D224" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" s="12" customFormat="1" ht="15">
+      <c r="A225" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B225" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C225" t="s">
+        <v>10</v>
+      </c>
+      <c r="D225" s="13">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="15">
+      <c r="A226" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C226" t="s">
+        <v>6</v>
+      </c>
+      <c r="D226" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B227" t="s">
+        <v>7</v>
+      </c>
+      <c r="C227" t="s">
+        <v>6</v>
+      </c>
+      <c r="D227" s="6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B228" t="s">
+        <v>5</v>
+      </c>
+      <c r="C228" t="s">
+        <v>8</v>
+      </c>
+      <c r="D228" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B229" t="s">
+        <v>7</v>
+      </c>
+      <c r="C229" t="s">
+        <v>8</v>
+      </c>
+      <c r="D229" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B230" t="s">
+        <v>5</v>
+      </c>
+      <c r="C230" t="s">
+        <v>9</v>
+      </c>
+      <c r="D230" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B231" t="s">
+        <v>7</v>
+      </c>
+      <c r="C231" t="s">
+        <v>9</v>
+      </c>
+      <c r="D231" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B232" t="s">
+        <v>5</v>
+      </c>
+      <c r="C232" t="s">
+        <v>10</v>
+      </c>
+      <c r="D232" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" s="12" customFormat="1">
+      <c r="A233" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B233" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C233" t="s">
+        <v>10</v>
+      </c>
+      <c r="D233" s="13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="15">
+      <c r="A234" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C234" t="s">
+        <v>6</v>
+      </c>
+      <c r="D234" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B235" t="s">
+        <v>7</v>
+      </c>
+      <c r="C235" t="s">
+        <v>6</v>
+      </c>
+      <c r="D235" s="6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B236" t="s">
+        <v>5</v>
+      </c>
+      <c r="C236" t="s">
+        <v>8</v>
+      </c>
+      <c r="D236" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B237" t="s">
+        <v>7</v>
+      </c>
+      <c r="C237" t="s">
+        <v>8</v>
+      </c>
+      <c r="D237" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B238" t="s">
+        <v>5</v>
+      </c>
+      <c r="C238" t="s">
+        <v>9</v>
+      </c>
+      <c r="D238" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B239" t="s">
+        <v>7</v>
+      </c>
+      <c r="C239" t="s">
+        <v>9</v>
+      </c>
+      <c r="D239" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B240" t="s">
+        <v>5</v>
+      </c>
+      <c r="C240" t="s">
+        <v>10</v>
+      </c>
+      <c r="D240" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" s="12" customFormat="1">
+      <c r="A241" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B241" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C241" t="s">
+        <v>10</v>
+      </c>
+      <c r="D241" s="13">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" ht="15">
+      <c r="A242" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C242" t="s">
+        <v>6</v>
+      </c>
+      <c r="D242" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" ht="15">
+      <c r="A243" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B243" t="s">
+        <v>7</v>
+      </c>
+      <c r="C243" t="s">
+        <v>6</v>
+      </c>
+      <c r="D243" s="6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" ht="15">
+      <c r="A244" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B244" t="s">
+        <v>5</v>
+      </c>
+      <c r="C244" t="s">
+        <v>8</v>
+      </c>
+      <c r="D244" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="15">
+      <c r="A245" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B245" t="s">
+        <v>7</v>
+      </c>
+      <c r="C245" t="s">
+        <v>8</v>
+      </c>
+      <c r="D245" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" ht="15">
+      <c r="A246" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B246" t="s">
+        <v>5</v>
+      </c>
+      <c r="C246" t="s">
+        <v>9</v>
+      </c>
+      <c r="D246" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" ht="15">
+      <c r="A247" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B247" t="s">
+        <v>7</v>
+      </c>
+      <c r="C247" t="s">
+        <v>9</v>
+      </c>
+      <c r="D247" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" ht="15">
+      <c r="A248" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B248" t="s">
+        <v>5</v>
+      </c>
+      <c r="C248" t="s">
+        <v>10</v>
+      </c>
+      <c r="D248" s="6">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" ht="15">
+      <c r="A249" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B249" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C249" t="s">
+        <v>10</v>
+      </c>
+      <c r="D249" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" ht="15">
+      <c r="A250" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D250" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" ht="15">
+      <c r="A251" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B251" t="s">
+        <v>7</v>
+      </c>
+      <c r="C251" t="s">
+        <v>6</v>
+      </c>
+      <c r="D251" s="6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" ht="15">
+      <c r="A252" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B252" t="s">
+        <v>5</v>
+      </c>
+      <c r="C252" t="s">
+        <v>8</v>
+      </c>
+      <c r="D252" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" ht="15">
+      <c r="A253" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B253" t="s">
+        <v>7</v>
+      </c>
+      <c r="C253" t="s">
+        <v>8</v>
+      </c>
+      <c r="D253" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" ht="15">
+      <c r="A254" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B254" t="s">
+        <v>5</v>
+      </c>
+      <c r="C254" t="s">
+        <v>9</v>
+      </c>
+      <c r="D254" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" ht="15">
+      <c r="A255" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B255" t="s">
+        <v>7</v>
+      </c>
+      <c r="C255" t="s">
+        <v>9</v>
+      </c>
+      <c r="D255" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" ht="15">
+      <c r="A256" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B256" t="s">
+        <v>5</v>
+      </c>
+      <c r="C256" t="s">
+        <v>10</v>
+      </c>
+      <c r="D256" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" ht="15">
+      <c r="A257" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B257" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C257" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D257" s="13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" ht="15">
+      <c r="A258" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B258" t="s">
+        <v>5</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D258" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" ht="15">
+      <c r="A259" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B259" t="s">
+        <v>7</v>
+      </c>
+      <c r="C259" t="s">
+        <v>6</v>
+      </c>
+      <c r="D259" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="15">
+      <c r="A260" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B260" t="s">
+        <v>5</v>
+      </c>
+      <c r="C260" t="s">
+        <v>8</v>
+      </c>
+      <c r="D260" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" ht="15">
+      <c r="A261" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B261" t="s">
+        <v>7</v>
+      </c>
+      <c r="C261" t="s">
+        <v>8</v>
+      </c>
+      <c r="D261" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" ht="15">
+      <c r="A262" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B262" t="s">
+        <v>5</v>
+      </c>
+      <c r="C262" t="s">
+        <v>9</v>
+      </c>
+      <c r="D262" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" ht="15">
+      <c r="A263" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B263" t="s">
+        <v>7</v>
+      </c>
+      <c r="C263" t="s">
+        <v>9</v>
+      </c>
+      <c r="D263" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" ht="15">
+      <c r="A264" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B264" t="s">
+        <v>5</v>
+      </c>
+      <c r="C264" t="s">
+        <v>10</v>
+      </c>
+      <c r="D264" s="6">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" ht="15">
+      <c r="A265" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B265" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C265" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D265" s="13">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" ht="15">
+      <c r="A266" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B266" t="s">
+        <v>5</v>
+      </c>
+      <c r="C266" t="s">
+        <v>6</v>
+      </c>
+      <c r="D266" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" ht="15">
+      <c r="A267" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B267" t="s">
+        <v>7</v>
+      </c>
+      <c r="C267" t="s">
+        <v>6</v>
+      </c>
+      <c r="D267" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" ht="15">
+      <c r="A268" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B268" t="s">
+        <v>5</v>
+      </c>
+      <c r="C268" t="s">
+        <v>8</v>
+      </c>
+      <c r="D268" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" ht="15">
+      <c r="A269" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B269" t="s">
+        <v>7</v>
+      </c>
+      <c r="C269" t="s">
+        <v>8</v>
+      </c>
+      <c r="D269" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" ht="15">
+      <c r="A270" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B270" t="s">
+        <v>5</v>
+      </c>
+      <c r="C270" t="s">
+        <v>9</v>
+      </c>
+      <c r="D270" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" ht="15">
+      <c r="A271" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B271" t="s">
+        <v>7</v>
+      </c>
+      <c r="C271" t="s">
+        <v>9</v>
+      </c>
+      <c r="D271" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" ht="15">
+      <c r="A272" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B272" t="s">
+        <v>5</v>
+      </c>
+      <c r="C272" t="s">
+        <v>10</v>
+      </c>
+      <c r="D272" s="6">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" ht="15">
+      <c r="A273" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B273" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C273" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D273" s="13">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" ht="15">
+      <c r="A274" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B274" t="s">
+        <v>5</v>
+      </c>
+      <c r="C274" t="s">
+        <v>6</v>
+      </c>
+      <c r="D274" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" ht="15">
+      <c r="A275" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B275" t="s">
+        <v>7</v>
+      </c>
+      <c r="C275" t="s">
+        <v>6</v>
+      </c>
+      <c r="D275" s="6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" ht="15">
+      <c r="A276" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B276" t="s">
+        <v>5</v>
+      </c>
+      <c r="C276" t="s">
+        <v>8</v>
+      </c>
+      <c r="D276" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" ht="15">
+      <c r="A277" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B277" t="s">
+        <v>7</v>
+      </c>
+      <c r="C277" t="s">
+        <v>8</v>
+      </c>
+      <c r="D277" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" ht="15">
+      <c r="A278" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B278" t="s">
+        <v>5</v>
+      </c>
+      <c r="C278" t="s">
+        <v>9</v>
+      </c>
+      <c r="D278" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="15">
+      <c r="A279" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B279" t="s">
+        <v>7</v>
+      </c>
+      <c r="C279" t="s">
+        <v>9</v>
+      </c>
+      <c r="D279" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" ht="15">
+      <c r="A280" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B280" t="s">
+        <v>5</v>
+      </c>
+      <c r="C280" t="s">
+        <v>10</v>
+      </c>
+      <c r="D280" s="6">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" ht="15">
+      <c r="A281" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B281" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C281" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D281" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="15">
+      <c r="A282" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B282" t="s">
+        <v>5</v>
+      </c>
+      <c r="C282" t="s">
+        <v>6</v>
+      </c>
+      <c r="D282" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" ht="15">
+      <c r="A283" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B283" t="s">
+        <v>7</v>
+      </c>
+      <c r="C283" t="s">
+        <v>6</v>
+      </c>
+      <c r="D283" s="6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" ht="15">
+      <c r="A284" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B284" t="s">
+        <v>5</v>
+      </c>
+      <c r="C284" t="s">
+        <v>8</v>
+      </c>
+      <c r="D284" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" ht="15">
+      <c r="A285" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B285" t="s">
+        <v>7</v>
+      </c>
+      <c r="C285" t="s">
+        <v>8</v>
+      </c>
+      <c r="D285" s="6">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" ht="15">
+      <c r="A286" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B286" t="s">
+        <v>5</v>
+      </c>
+      <c r="C286" t="s">
+        <v>9</v>
+      </c>
+      <c r="D286" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" ht="15">
+      <c r="A287" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B287" t="s">
+        <v>7</v>
+      </c>
+      <c r="C287" t="s">
+        <v>9</v>
+      </c>
+      <c r="D287" s="6">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" ht="15">
+      <c r="A288" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B288" t="s">
+        <v>5</v>
+      </c>
+      <c r="C288" t="s">
+        <v>10</v>
+      </c>
+      <c r="D288" s="6">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="15">
+      <c r="A289" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B289" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C289" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D289" s="13">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="15">
+      <c r="A290" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B290" t="s">
+        <v>5</v>
+      </c>
+      <c r="C290" t="s">
+        <v>6</v>
+      </c>
+      <c r="D290" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="15">
+      <c r="A291" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B291" t="s">
+        <v>7</v>
+      </c>
+      <c r="C291" t="s">
+        <v>6</v>
+      </c>
+      <c r="D291" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" ht="15">
+      <c r="A292" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B292" t="s">
+        <v>5</v>
+      </c>
+      <c r="C292" t="s">
+        <v>8</v>
+      </c>
+      <c r="D292" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" ht="15">
+      <c r="A293" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B293" t="s">
+        <v>7</v>
+      </c>
+      <c r="C293" t="s">
+        <v>8</v>
+      </c>
+      <c r="D293" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" ht="15">
+      <c r="A294" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B294" t="s">
+        <v>5</v>
+      </c>
+      <c r="C294" t="s">
+        <v>9</v>
+      </c>
+      <c r="D294" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" ht="15">
+      <c r="A295" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B295" t="s">
+        <v>7</v>
+      </c>
+      <c r="C295" t="s">
+        <v>9</v>
+      </c>
+      <c r="D295" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" ht="15">
+      <c r="A296" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B296" t="s">
+        <v>5</v>
+      </c>
+      <c r="C296" t="s">
+        <v>10</v>
+      </c>
+      <c r="D296" s="6">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="15">
+      <c r="A297" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B297" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C297" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D297" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" ht="15">
+      <c r="A298" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B298" t="s">
+        <v>5</v>
+      </c>
+      <c r="C298" t="s">
+        <v>6</v>
+      </c>
+      <c r="D298" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" ht="15">
+      <c r="A299" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B299" t="s">
+        <v>7</v>
+      </c>
+      <c r="C299" t="s">
+        <v>6</v>
+      </c>
+      <c r="D299" s="6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="15">
+      <c r="A300" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B300" t="s">
+        <v>5</v>
+      </c>
+      <c r="C300" t="s">
+        <v>8</v>
+      </c>
+      <c r="D300" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" ht="15">
+      <c r="A301" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B301" t="s">
+        <v>7</v>
+      </c>
+      <c r="C301" t="s">
+        <v>8</v>
+      </c>
+      <c r="D301" s="6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" ht="15">
+      <c r="A302" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B302" t="s">
+        <v>5</v>
+      </c>
+      <c r="C302" t="s">
+        <v>9</v>
+      </c>
+      <c r="D302" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" ht="15">
+      <c r="A303" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B303" t="s">
+        <v>7</v>
+      </c>
+      <c r="C303" t="s">
+        <v>9</v>
+      </c>
+      <c r="D303" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" ht="15">
+      <c r="A304" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B304" t="s">
+        <v>5</v>
+      </c>
+      <c r="C304" t="s">
+        <v>10</v>
+      </c>
+      <c r="D304" s="6">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" ht="15">
+      <c r="A305" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B305" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C305" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D305" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" ht="15">
+      <c r="A306" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B306" t="s">
+        <v>5</v>
+      </c>
+      <c r="C306" t="s">
+        <v>6</v>
+      </c>
+      <c r="D306" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" ht="15">
+      <c r="A307" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B307" t="s">
+        <v>7</v>
+      </c>
+      <c r="C307" t="s">
+        <v>6</v>
+      </c>
+      <c r="D307" s="6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" ht="15">
+      <c r="A308" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B308" t="s">
+        <v>5</v>
+      </c>
+      <c r="C308" t="s">
+        <v>8</v>
+      </c>
+      <c r="D308" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" ht="15">
+      <c r="A309" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B309" t="s">
+        <v>7</v>
+      </c>
+      <c r="C309" t="s">
+        <v>8</v>
+      </c>
+      <c r="D309" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" ht="15">
+      <c r="A310" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B310" t="s">
+        <v>5</v>
+      </c>
+      <c r="C310" t="s">
+        <v>9</v>
+      </c>
+      <c r="D310" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" ht="15">
+      <c r="A311" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B311" t="s">
+        <v>7</v>
+      </c>
+      <c r="C311" t="s">
+        <v>9</v>
+      </c>
+      <c r="D311" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" ht="15">
+      <c r="A312" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B312" t="s">
+        <v>5</v>
+      </c>
+      <c r="C312" t="s">
+        <v>10</v>
+      </c>
+      <c r="D312" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" ht="15">
+      <c r="A313" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B313" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C313" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D313" s="13">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" ht="15">
+      <c r="A314" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B314" t="s">
+        <v>5</v>
+      </c>
+      <c r="C314" t="s">
+        <v>6</v>
+      </c>
+      <c r="D314" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" ht="15">
+      <c r="A315" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B315" t="s">
+        <v>7</v>
+      </c>
+      <c r="C315" t="s">
+        <v>6</v>
+      </c>
+      <c r="D315" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" ht="15">
+      <c r="A316" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B316" t="s">
+        <v>5</v>
+      </c>
+      <c r="C316" t="s">
+        <v>8</v>
+      </c>
+      <c r="D316" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" ht="15">
+      <c r="A317" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B317" t="s">
+        <v>7</v>
+      </c>
+      <c r="C317" t="s">
+        <v>8</v>
+      </c>
+      <c r="D317" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" ht="15">
+      <c r="A318" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B318" t="s">
+        <v>5</v>
+      </c>
+      <c r="C318" t="s">
+        <v>9</v>
+      </c>
+      <c r="D318" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" ht="15">
+      <c r="A319" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B319" t="s">
+        <v>7</v>
+      </c>
+      <c r="C319" t="s">
+        <v>9</v>
+      </c>
+      <c r="D319" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" ht="15">
+      <c r="A320" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B320" t="s">
+        <v>5</v>
+      </c>
+      <c r="C320" t="s">
+        <v>10</v>
+      </c>
+      <c r="D320" s="6">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" ht="15">
+      <c r="A321" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B321" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C321" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D321" s="13">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" ht="15">
+      <c r="A322" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B322" t="s">
+        <v>5</v>
+      </c>
+      <c r="C322" t="s">
+        <v>6</v>
+      </c>
+      <c r="D322" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" ht="15">
+      <c r="A323" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B323" t="s">
+        <v>7</v>
+      </c>
+      <c r="C323" t="s">
+        <v>6</v>
+      </c>
+      <c r="D323" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" ht="15">
+      <c r="A324" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B324" t="s">
+        <v>5</v>
+      </c>
+      <c r="C324" t="s">
+        <v>8</v>
+      </c>
+      <c r="D324" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" ht="15">
+      <c r="A325" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B325" t="s">
+        <v>7</v>
+      </c>
+      <c r="C325" t="s">
+        <v>8</v>
+      </c>
+      <c r="D325" s="6">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" ht="15">
+      <c r="A326" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B326" t="s">
+        <v>5</v>
+      </c>
+      <c r="C326" t="s">
+        <v>9</v>
+      </c>
+      <c r="D326" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" ht="15">
+      <c r="A327" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B327" t="s">
+        <v>7</v>
+      </c>
+      <c r="C327" t="s">
+        <v>9</v>
+      </c>
+      <c r="D327" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" ht="15">
+      <c r="A328" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B328" t="s">
+        <v>5</v>
+      </c>
+      <c r="C328" t="s">
+        <v>10</v>
+      </c>
+      <c r="D328" s="6">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" ht="15">
+      <c r="A329" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B329" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C329" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D329" s="13">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" ht="15">
+      <c r="A330" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B330" t="s">
+        <v>5</v>
+      </c>
+      <c r="C330" t="s">
+        <v>6</v>
+      </c>
+      <c r="D330" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" ht="15">
+      <c r="A331" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B331" t="s">
+        <v>7</v>
+      </c>
+      <c r="C331" t="s">
+        <v>6</v>
+      </c>
+      <c r="D331" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" ht="15">
+      <c r="A332" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B332" t="s">
+        <v>5</v>
+      </c>
+      <c r="C332" t="s">
+        <v>8</v>
+      </c>
+      <c r="D332" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" ht="15">
+      <c r="A333" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B333" t="s">
+        <v>7</v>
+      </c>
+      <c r="C333" t="s">
+        <v>8</v>
+      </c>
+      <c r="D333" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" ht="15">
+      <c r="A334" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B334" t="s">
+        <v>5</v>
+      </c>
+      <c r="C334" t="s">
+        <v>9</v>
+      </c>
+      <c r="D334" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" ht="15">
+      <c r="A335" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B335" t="s">
+        <v>7</v>
+      </c>
+      <c r="C335" t="s">
+        <v>9</v>
+      </c>
+      <c r="D335" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" ht="15">
+      <c r="A336" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B336" t="s">
+        <v>5</v>
+      </c>
+      <c r="C336" t="s">
+        <v>10</v>
+      </c>
+      <c r="D336" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" ht="15">
+      <c r="A337" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B337" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C337" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D337" s="13">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" ht="15">
+      <c r="A338" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B338" t="s">
+        <v>5</v>
+      </c>
+      <c r="C338" t="s">
+        <v>6</v>
+      </c>
+      <c r="D338" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" ht="15">
+      <c r="A339" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B339" t="s">
+        <v>7</v>
+      </c>
+      <c r="C339" t="s">
+        <v>6</v>
+      </c>
+      <c r="D339" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" ht="15">
+      <c r="A340" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B340" t="s">
+        <v>5</v>
+      </c>
+      <c r="C340" t="s">
+        <v>8</v>
+      </c>
+      <c r="D340" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" ht="15">
+      <c r="A341" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B341" t="s">
+        <v>7</v>
+      </c>
+      <c r="C341" t="s">
+        <v>8</v>
+      </c>
+      <c r="D341" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" ht="15">
+      <c r="A342" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B342" t="s">
+        <v>5</v>
+      </c>
+      <c r="C342" t="s">
+        <v>9</v>
+      </c>
+      <c r="D342" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" ht="15">
+      <c r="A343" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B343" t="s">
+        <v>7</v>
+      </c>
+      <c r="C343" t="s">
+        <v>9</v>
+      </c>
+      <c r="D343" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" ht="15">
+      <c r="A344" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B344" t="s">
+        <v>5</v>
+      </c>
+      <c r="C344" t="s">
+        <v>10</v>
+      </c>
+      <c r="D344" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" ht="15">
+      <c r="A345" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B345" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C345" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D345" s="13">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" ht="15">
+      <c r="A346" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B346" t="s">
+        <v>5</v>
+      </c>
+      <c r="C346" t="s">
+        <v>6</v>
+      </c>
+      <c r="D346" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" ht="15">
+      <c r="A347" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B347" t="s">
+        <v>7</v>
+      </c>
+      <c r="C347" t="s">
+        <v>6</v>
+      </c>
+      <c r="D347" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" ht="15">
+      <c r="A348" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B348" t="s">
+        <v>5</v>
+      </c>
+      <c r="C348" t="s">
+        <v>8</v>
+      </c>
+      <c r="D348" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" ht="15">
+      <c r="A349" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B349" t="s">
+        <v>7</v>
+      </c>
+      <c r="C349" t="s">
+        <v>8</v>
+      </c>
+      <c r="D349" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" ht="15">
+      <c r="A350" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B350" t="s">
+        <v>5</v>
+      </c>
+      <c r="C350" t="s">
+        <v>9</v>
+      </c>
+      <c r="D350" s="6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" ht="15">
+      <c r="A351" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B351" t="s">
+        <v>7</v>
+      </c>
+      <c r="C351" t="s">
+        <v>9</v>
+      </c>
+      <c r="D351" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" ht="15">
+      <c r="A352" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B352" t="s">
+        <v>5</v>
+      </c>
+      <c r="C352" t="s">
+        <v>10</v>
+      </c>
+      <c r="D352" s="6">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" ht="15">
+      <c r="A353" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B353" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C353" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D353" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" ht="15">
+      <c r="A354" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B354" t="s">
+        <v>5</v>
+      </c>
+      <c r="C354" t="s">
+        <v>6</v>
+      </c>
+      <c r="D354" s="6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" ht="15">
+      <c r="A355" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B355" t="s">
+        <v>7</v>
+      </c>
+      <c r="C355" t="s">
+        <v>6</v>
+      </c>
+      <c r="D355" s="6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" ht="15">
+      <c r="A356" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B356" t="s">
+        <v>5</v>
+      </c>
+      <c r="C356" t="s">
+        <v>8</v>
+      </c>
+      <c r="D356" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" ht="15">
+      <c r="A357" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B357" t="s">
+        <v>7</v>
+      </c>
+      <c r="C357" t="s">
+        <v>8</v>
+      </c>
+      <c r="D357" s="6">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" ht="15">
+      <c r="A358" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B358" t="s">
+        <v>5</v>
+      </c>
+      <c r="C358" t="s">
+        <v>9</v>
+      </c>
+      <c r="D358" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" ht="15">
+      <c r="A359" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B359" t="s">
+        <v>7</v>
+      </c>
+      <c r="C359" t="s">
+        <v>9</v>
+      </c>
+      <c r="D359" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" ht="15">
+      <c r="A360" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B360" t="s">
+        <v>5</v>
+      </c>
+      <c r="C360" t="s">
+        <v>10</v>
+      </c>
+      <c r="D360" s="6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" ht="15">
+      <c r="A361" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B361" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C361" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D361" s="13">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" ht="15"/>
+    <row r="363" spans="1:4" ht="15"/>
+    <row r="364" spans="1:4" ht="15"/>
+    <row r="365" spans="1:4" ht="15"/>
+    <row r="366" spans="1:4" ht="15"/>
+    <row r="367" spans="1:4" ht="15"/>
+    <row r="368" spans="1:4" ht="15"/>
+    <row r="369" ht="15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2380,8 +5759,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006131D81E7FE36E44885B3A04523FCF5D" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3c9ab67dcfa560232a36bfe42a1cf3da">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71842362-ab5d-46b4-b35f-08dc9c6328ce" xmlns:ns3="8def90a7-5747-4395-b698-a599996d7912" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="85c6a7f5c224f550ecad7291476c1ef0" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006131D81E7FE36E44885B3A04523FCF5D" ma:contentTypeVersion="14" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8f9efaeda295997044994eea58453835">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71842362-ab5d-46b4-b35f-08dc9c6328ce" xmlns:ns3="8def90a7-5747-4395-b698-a599996d7912" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7a2e7ed8b28d563a97a27396956f6ac0" ns2:_="" ns3:_="">
     <xsd:import namespace="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
     <xsd:import namespace="8def90a7-5747-4395-b698-a599996d7912"/>
     <xsd:element name="properties">
@@ -2428,7 +5807,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="eaf58ba8-1e8d-4aec-a6f5-993f6032dc74" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Afbeeldingtags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="eaf58ba8-1e8d-4aec-a6f5-993f6032dc74" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -2482,7 +5861,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Gedeeld met" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -2501,7 +5880,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Gedeeld met details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -2518,8 +5897,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhoudstype"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -2624,7 +6003,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{211CAD49-E595-42C4-9A3A-5B665001F655}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79464CFF-4EB4-4262-9D1E-A0E9F07A9D35}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/raw/expert_scores.xlsx
+++ b/data/raw/expert_scores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universiteittwente.sharepoint.com/sites/Stress-in-Action/Gedeelde documenten/General/_Relational - SiA-WD/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxu567\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76F443B9-2CFB-4DCD-9AF3-787198A5CAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0221BBD-DA81-4FE9-A6B4-94FFE6BC2EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{2C9CAB11-EC45-49EE-BE20-1107D0FD28A6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C9CAB11-EC45-49EE-BE20-1107D0FD28A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="64">
   <si>
     <t>device_id</t>
   </si>
@@ -211,12 +211,30 @@
   <si>
     <t>045_sia_wd_med</t>
   </si>
+  <si>
+    <t>046_sia_wd_rin</t>
+  </si>
+  <si>
+    <t>047_sia_wd_ult</t>
+  </si>
+  <si>
+    <t>048_sia_wd_nua</t>
+  </si>
+  <si>
+    <t>049_sia_wd_cos</t>
+  </si>
+  <si>
+    <t>050_sia_wd_lum</t>
+  </si>
+  <si>
+    <t>051_sia_wd_plu</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,7 +265,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -659,19 +677,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52AC09CD-A4FA-4E91-BDBC-BF7CF9B4D46E}">
-  <dimension ref="A1:G369"/>
-  <sheetFormatPr defaultRowHeight="14.65"/>
+  <dimension ref="A1:G409"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="6" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="32.28515625" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="32.33203125" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -685,7 +703,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -700,7 +718,7 @@
       </c>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -715,7 +733,7 @@
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -730,7 +748,7 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -745,7 +763,7 @@
       </c>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -760,7 +778,7 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -775,7 +793,7 @@
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -790,7 +808,7 @@
       </c>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -805,7 +823,7 @@
       </c>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" s="2" customFormat="1">
+    <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -820,7 +838,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -835,7 +853,7 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -849,7 +867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -863,7 +881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -877,7 +895,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -891,7 +909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -905,7 +923,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="8" customFormat="1">
+    <row r="17" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>13</v>
       </c>
@@ -919,7 +937,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>15</v>
       </c>
@@ -933,7 +951,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>15</v>
       </c>
@@ -947,7 +965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>15</v>
       </c>
@@ -961,7 +979,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>15</v>
       </c>
@@ -975,7 +993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>15</v>
       </c>
@@ -989,7 +1007,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>15</v>
       </c>
@@ -1003,7 +1021,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>15</v>
       </c>
@@ -1017,7 +1035,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="8" customFormat="1">
+    <row r="25" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>15</v>
       </c>
@@ -1031,7 +1049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>16</v>
       </c>
@@ -1045,7 +1063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>16</v>
       </c>
@@ -1059,7 +1077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>16</v>
       </c>
@@ -1073,7 +1091,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>16</v>
       </c>
@@ -1087,7 +1105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>16</v>
       </c>
@@ -1101,7 +1119,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>16</v>
       </c>
@@ -1115,7 +1133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>16</v>
       </c>
@@ -1129,7 +1147,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="33" spans="1:4" s="8" customFormat="1">
+    <row r="33" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>16</v>
       </c>
@@ -1143,7 +1161,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>17</v>
       </c>
@@ -1157,7 +1175,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>17</v>
       </c>
@@ -1171,7 +1189,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>17</v>
       </c>
@@ -1185,7 +1203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>17</v>
       </c>
@@ -1199,7 +1217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
         <v>17</v>
       </c>
@@ -1213,7 +1231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>17</v>
       </c>
@@ -1227,7 +1245,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>17</v>
       </c>
@@ -1241,7 +1259,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="41" spans="1:4" s="8" customFormat="1">
+    <row r="41" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>17</v>
       </c>
@@ -1255,7 +1273,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>18</v>
       </c>
@@ -1269,7 +1287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
         <v>18</v>
       </c>
@@ -1283,7 +1301,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>18</v>
       </c>
@@ -1297,7 +1315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>18</v>
       </c>
@@ -1311,7 +1329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>18</v>
       </c>
@@ -1325,7 +1343,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>18</v>
       </c>
@@ -1339,7 +1357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>18</v>
       </c>
@@ -1353,7 +1371,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="49" spans="1:4" s="8" customFormat="1">
+    <row r="49" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>18</v>
       </c>
@@ -1367,7 +1385,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>19</v>
       </c>
@@ -1381,7 +1399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>19</v>
       </c>
@@ -1395,7 +1413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>19</v>
       </c>
@@ -1409,7 +1427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>19</v>
       </c>
@@ -1423,7 +1441,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>19</v>
       </c>
@@ -1437,7 +1455,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>19</v>
       </c>
@@ -1451,7 +1469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
         <v>19</v>
       </c>
@@ -1465,7 +1483,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="57" spans="1:4" s="8" customFormat="1">
+    <row r="57" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
         <v>19</v>
       </c>
@@ -1479,7 +1497,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>20</v>
       </c>
@@ -1493,7 +1511,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
         <v>20</v>
       </c>
@@ -1507,7 +1525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
         <v>20</v>
       </c>
@@ -1521,7 +1539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
         <v>20</v>
       </c>
@@ -1535,7 +1553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>20</v>
       </c>
@@ -1549,7 +1567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
         <v>20</v>
       </c>
@@ -1563,7 +1581,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
         <v>20</v>
       </c>
@@ -1577,7 +1595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:4" s="8" customFormat="1">
+    <row r="65" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
         <v>20</v>
       </c>
@@ -1591,7 +1609,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
         <v>21</v>
       </c>
@@ -1605,7 +1623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
         <v>21</v>
       </c>
@@ -1619,7 +1637,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="10" t="s">
         <v>21</v>
       </c>
@@ -1633,7 +1651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>21</v>
       </c>
@@ -1647,7 +1665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="10" t="s">
         <v>21</v>
       </c>
@@ -1661,7 +1679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
         <v>21</v>
       </c>
@@ -1675,7 +1693,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="10" t="s">
         <v>21</v>
       </c>
@@ -1689,7 +1707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:4" s="8" customFormat="1">
+    <row r="73" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
         <v>21</v>
       </c>
@@ -1703,7 +1721,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="10" t="s">
         <v>22</v>
       </c>
@@ -1717,7 +1735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
         <v>22</v>
       </c>
@@ -1731,7 +1749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
         <v>22</v>
       </c>
@@ -1745,7 +1763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="10" t="s">
         <v>22</v>
       </c>
@@ -1759,7 +1777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="10" t="s">
         <v>22</v>
       </c>
@@ -1773,7 +1791,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="10" t="s">
         <v>22</v>
       </c>
@@ -1787,7 +1805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
         <v>22</v>
       </c>
@@ -1801,7 +1819,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:4" s="8" customFormat="1">
+    <row r="81" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="11" t="s">
         <v>22</v>
       </c>
@@ -1815,7 +1833,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
         <v>23</v>
       </c>
@@ -1829,7 +1847,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="10" t="s">
         <v>23</v>
       </c>
@@ -1843,7 +1861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
         <v>23</v>
       </c>
@@ -1857,7 +1875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="10" t="s">
         <v>23</v>
       </c>
@@ -1871,7 +1889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="10" t="s">
         <v>23</v>
       </c>
@@ -1885,7 +1903,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="10" t="s">
         <v>23</v>
       </c>
@@ -1899,7 +1917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="10" t="s">
         <v>23</v>
       </c>
@@ -1913,7 +1931,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="89" spans="1:4" s="8" customFormat="1">
+    <row r="89" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="11" t="s">
         <v>23</v>
       </c>
@@ -1927,7 +1945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="10" t="s">
         <v>24</v>
       </c>
@@ -1941,7 +1959,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="10" t="s">
         <v>24</v>
       </c>
@@ -1955,7 +1973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
         <v>24</v>
       </c>
@@ -1969,7 +1987,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="10" t="s">
         <v>24</v>
       </c>
@@ -1983,7 +2001,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="10" t="s">
         <v>24</v>
       </c>
@@ -1997,7 +2015,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
         <v>24</v>
       </c>
@@ -2011,7 +2029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="10" t="s">
         <v>24</v>
       </c>
@@ -2025,7 +2043,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="97" spans="1:4" s="8" customFormat="1">
+    <row r="97" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
         <v>24</v>
       </c>
@@ -2039,7 +2057,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
         <v>25</v>
       </c>
@@ -2053,7 +2071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="10" t="s">
         <v>25</v>
       </c>
@@ -2067,7 +2085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="10" t="s">
         <v>25</v>
       </c>
@@ -2081,7 +2099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="10" t="s">
         <v>25</v>
       </c>
@@ -2095,7 +2113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
         <v>25</v>
       </c>
@@ -2109,7 +2127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="10" t="s">
         <v>25</v>
       </c>
@@ -2123,7 +2141,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="10" t="s">
         <v>25</v>
       </c>
@@ -2137,7 +2155,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="105" spans="1:4" s="8" customFormat="1">
+    <row r="105" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="11" t="s">
         <v>25</v>
       </c>
@@ -2151,7 +2169,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="10" t="s">
         <v>26</v>
       </c>
@@ -2165,7 +2183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
         <v>26</v>
       </c>
@@ -2179,7 +2197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="10" t="s">
         <v>26</v>
       </c>
@@ -2193,7 +2211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="10" t="s">
         <v>26</v>
       </c>
@@ -2207,7 +2225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="10" t="s">
         <v>26</v>
       </c>
@@ -2221,7 +2239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="10" t="s">
         <v>26</v>
       </c>
@@ -2235,7 +2253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="10" t="s">
         <v>26</v>
       </c>
@@ -2249,7 +2267,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:4" s="8" customFormat="1">
+    <row r="113" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A113" s="11" t="s">
         <v>26</v>
       </c>
@@ -2263,7 +2281,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="10" t="s">
         <v>27</v>
       </c>
@@ -2277,7 +2295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="10" t="s">
         <v>27</v>
       </c>
@@ -2291,7 +2309,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
         <v>27</v>
       </c>
@@ -2305,7 +2323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
         <v>27</v>
       </c>
@@ -2319,7 +2337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="10" t="s">
         <v>27</v>
       </c>
@@ -2333,7 +2351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="10" t="s">
         <v>27</v>
       </c>
@@ -2347,7 +2365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="10" t="s">
         <v>27</v>
       </c>
@@ -2361,7 +2379,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="121" spans="1:4" s="8" customFormat="1">
+    <row r="121" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="11" t="s">
         <v>27</v>
       </c>
@@ -2375,7 +2393,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="15">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="10" t="s">
         <v>28</v>
       </c>
@@ -2389,7 +2407,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="10" t="s">
         <v>28</v>
       </c>
@@ -2403,7 +2421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="10" t="s">
         <v>28</v>
       </c>
@@ -2417,7 +2435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="10" t="s">
         <v>28</v>
       </c>
@@ -2431,7 +2449,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="10" t="s">
         <v>28</v>
       </c>
@@ -2445,7 +2463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="10" t="s">
         <v>28</v>
       </c>
@@ -2459,7 +2477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="10" t="s">
         <v>28</v>
       </c>
@@ -2473,7 +2491,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="129" spans="1:4" s="12" customFormat="1">
+    <row r="129" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="10" t="s">
         <v>28</v>
       </c>
@@ -2487,7 +2505,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="15">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="10" t="s">
         <v>29</v>
       </c>
@@ -2501,7 +2519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="10" t="s">
         <v>29</v>
       </c>
@@ -2515,7 +2533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="10" t="s">
         <v>29</v>
       </c>
@@ -2529,7 +2547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="10" t="s">
         <v>29</v>
       </c>
@@ -2543,7 +2561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="10" t="s">
         <v>29</v>
       </c>
@@ -2557,7 +2575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="10" t="s">
         <v>29</v>
       </c>
@@ -2571,7 +2589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="10" t="s">
         <v>29</v>
       </c>
@@ -2585,7 +2603,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:4" s="12" customFormat="1">
+    <row r="137" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="10" t="s">
         <v>29</v>
       </c>
@@ -2599,7 +2617,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="15">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="10" t="s">
         <v>30</v>
       </c>
@@ -2613,7 +2631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="10" t="s">
         <v>30</v>
       </c>
@@ -2627,7 +2645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="10" t="s">
         <v>30</v>
       </c>
@@ -2641,7 +2659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="10" t="s">
         <v>30</v>
       </c>
@@ -2655,7 +2673,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="10" t="s">
         <v>30</v>
       </c>
@@ -2669,7 +2687,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="10" t="s">
         <v>30</v>
       </c>
@@ -2683,7 +2701,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="10" t="s">
         <v>30</v>
       </c>
@@ -2697,7 +2715,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="145" spans="1:4" s="12" customFormat="1">
+    <row r="145" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A145" s="10" t="s">
         <v>30</v>
       </c>
@@ -2711,7 +2729,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="15">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="10" t="s">
         <v>31</v>
       </c>
@@ -2725,7 +2743,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="10" t="s">
         <v>31</v>
       </c>
@@ -2739,7 +2757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="10" t="s">
         <v>31</v>
       </c>
@@ -2753,7 +2771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="10" t="s">
         <v>31</v>
       </c>
@@ -2767,7 +2785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="10" t="s">
         <v>31</v>
       </c>
@@ -2781,7 +2799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="10" t="s">
         <v>31</v>
       </c>
@@ -2795,7 +2813,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="10" t="s">
         <v>31</v>
       </c>
@@ -2809,7 +2827,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="153" spans="1:4" s="12" customFormat="1">
+    <row r="153" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A153" s="10" t="s">
         <v>31</v>
       </c>
@@ -2823,7 +2841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="15">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="10" t="s">
         <v>32</v>
       </c>
@@ -2837,7 +2855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="10" t="s">
         <v>32</v>
       </c>
@@ -2851,7 +2869,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="10" t="s">
         <v>32</v>
       </c>
@@ -2865,7 +2883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="10" t="s">
         <v>32</v>
       </c>
@@ -2879,7 +2897,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="10" t="s">
         <v>32</v>
       </c>
@@ -2893,7 +2911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="10" t="s">
         <v>32</v>
       </c>
@@ -2907,7 +2925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="10" t="s">
         <v>32</v>
       </c>
@@ -2921,7 +2939,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="161" spans="1:4" s="12" customFormat="1">
+    <row r="161" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A161" s="10" t="s">
         <v>32</v>
       </c>
@@ -2935,7 +2953,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="15">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="10" t="s">
         <v>33</v>
       </c>
@@ -2949,7 +2967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="10" t="s">
         <v>33</v>
       </c>
@@ -2963,7 +2981,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="10" t="s">
         <v>33</v>
       </c>
@@ -2977,7 +2995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="10" t="s">
         <v>33</v>
       </c>
@@ -2991,7 +3009,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="10" t="s">
         <v>33</v>
       </c>
@@ -3005,7 +3023,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="10" t="s">
         <v>33</v>
       </c>
@@ -3019,7 +3037,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:4">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="10" t="s">
         <v>33</v>
       </c>
@@ -3033,7 +3051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" s="12" customFormat="1">
+    <row r="169" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A169" s="10" t="s">
         <v>33</v>
       </c>
@@ -3047,7 +3065,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="15">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="10" t="s">
         <v>34</v>
       </c>
@@ -3061,7 +3079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:4">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="10" t="s">
         <v>34</v>
       </c>
@@ -3075,7 +3093,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:4">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="10" t="s">
         <v>34</v>
       </c>
@@ -3089,7 +3107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:4">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="10" t="s">
         <v>34</v>
       </c>
@@ -3103,7 +3121,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:4">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="10" t="s">
         <v>34</v>
       </c>
@@ -3117,7 +3135,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:4">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="10" t="s">
         <v>34</v>
       </c>
@@ -3131,7 +3149,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:4">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="10" t="s">
         <v>34</v>
       </c>
@@ -3145,7 +3163,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="177" spans="1:4" s="12" customFormat="1">
+    <row r="177" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A177" s="10" t="s">
         <v>34</v>
       </c>
@@ -3159,7 +3177,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="15">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="10" t="s">
         <v>35</v>
       </c>
@@ -3173,7 +3191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:4">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="10" t="s">
         <v>35</v>
       </c>
@@ -3187,7 +3205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:4">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="10" t="s">
         <v>35</v>
       </c>
@@ -3201,7 +3219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:4">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="10" t="s">
         <v>35</v>
       </c>
@@ -3215,7 +3233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:4">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="10" t="s">
         <v>35</v>
       </c>
@@ -3229,7 +3247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:4">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="10" t="s">
         <v>35</v>
       </c>
@@ -3243,7 +3261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:4">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="10" t="s">
         <v>35</v>
       </c>
@@ -3257,7 +3275,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="185" spans="1:4" s="12" customFormat="1">
+    <row r="185" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A185" s="10" t="s">
         <v>35</v>
       </c>
@@ -3271,7 +3289,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="15">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="15" t="s">
         <v>36</v>
       </c>
@@ -3285,7 +3303,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="15">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="15" t="s">
         <v>36</v>
       </c>
@@ -3299,7 +3317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="15">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="15" t="s">
         <v>36</v>
       </c>
@@ -3313,7 +3331,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="15">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="15" t="s">
         <v>36</v>
       </c>
@@ -3327,7 +3345,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="15">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="15" t="s">
         <v>36</v>
       </c>
@@ -3341,7 +3359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="15">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="15" t="s">
         <v>36</v>
       </c>
@@ -3355,7 +3373,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="15">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="15" t="s">
         <v>36</v>
       </c>
@@ -3369,7 +3387,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="193" spans="1:4" s="12" customFormat="1" ht="15">
+    <row r="193" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A193" s="15" t="s">
         <v>36</v>
       </c>
@@ -3383,7 +3401,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="15">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="15" t="s">
         <v>37</v>
       </c>
@@ -3397,7 +3415,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="15">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="15" t="s">
         <v>37</v>
       </c>
@@ -3411,7 +3429,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="15">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="15" t="s">
         <v>37</v>
       </c>
@@ -3425,7 +3443,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="15">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="15" t="s">
         <v>37</v>
       </c>
@@ -3439,7 +3457,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="15">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="15" t="s">
         <v>37</v>
       </c>
@@ -3453,7 +3471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="15">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="15" t="s">
         <v>37</v>
       </c>
@@ -3467,7 +3485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="15">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="15" t="s">
         <v>37</v>
       </c>
@@ -3481,7 +3499,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="201" spans="1:4" s="12" customFormat="1" ht="15">
+    <row r="201" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A201" s="15" t="s">
         <v>37</v>
       </c>
@@ -3495,7 +3513,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="15">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="10" t="s">
         <v>38</v>
       </c>
@@ -3509,7 +3527,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:4">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="10" t="s">
         <v>38</v>
       </c>
@@ -3523,7 +3541,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="204" spans="1:4">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="10" t="s">
         <v>38</v>
       </c>
@@ -3537,7 +3555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:4">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="10" t="s">
         <v>38</v>
       </c>
@@ -3551,7 +3569,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:4">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="10" t="s">
         <v>38</v>
       </c>
@@ -3565,7 +3583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:4">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="10" t="s">
         <v>38</v>
       </c>
@@ -3579,7 +3597,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="208" spans="1:4">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="10" t="s">
         <v>38</v>
       </c>
@@ -3593,7 +3611,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="209" spans="1:4" s="12" customFormat="1">
+    <row r="209" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A209" s="10" t="s">
         <v>38</v>
       </c>
@@ -3607,7 +3625,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="15">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="10" t="s">
         <v>39</v>
       </c>
@@ -3621,7 +3639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:4">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="10" t="s">
         <v>39</v>
       </c>
@@ -3635,7 +3653,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="212" spans="1:4">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="10" t="s">
         <v>39</v>
       </c>
@@ -3649,7 +3667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:4">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="10" t="s">
         <v>39</v>
       </c>
@@ -3663,7 +3681,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:4">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="10" t="s">
         <v>39</v>
       </c>
@@ -3677,7 +3695,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:4">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="10" t="s">
         <v>39</v>
       </c>
@@ -3691,7 +3709,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="216" spans="1:4">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="10" t="s">
         <v>39</v>
       </c>
@@ -3705,7 +3723,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="217" spans="1:4" s="12" customFormat="1">
+    <row r="217" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A217" s="10" t="s">
         <v>39</v>
       </c>
@@ -3719,7 +3737,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="15">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="15" t="s">
         <v>40</v>
       </c>
@@ -3733,7 +3751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="15">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="15" t="s">
         <v>40</v>
       </c>
@@ -3747,7 +3765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="15">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="15" t="s">
         <v>40</v>
       </c>
@@ -3761,7 +3779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="15">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="15" t="s">
         <v>40</v>
       </c>
@@ -3775,7 +3793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="15">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="15" t="s">
         <v>40</v>
       </c>
@@ -3789,7 +3807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="15">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="15" t="s">
         <v>40</v>
       </c>
@@ -3803,7 +3821,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="15">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="15" t="s">
         <v>40</v>
       </c>
@@ -3817,7 +3835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:4" s="12" customFormat="1" ht="15">
+    <row r="225" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A225" s="15" t="s">
         <v>40</v>
       </c>
@@ -3831,7 +3849,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="15">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="10" t="s">
         <v>41</v>
       </c>
@@ -3845,7 +3863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:4">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="10" t="s">
         <v>41</v>
       </c>
@@ -3859,7 +3877,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="228" spans="1:4">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="10" t="s">
         <v>41</v>
       </c>
@@ -3873,7 +3891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:4">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="10" t="s">
         <v>41</v>
       </c>
@@ -3887,7 +3905,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="10" t="s">
         <v>41</v>
       </c>
@@ -3901,7 +3919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:4">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="10" t="s">
         <v>41</v>
       </c>
@@ -3915,7 +3933,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="232" spans="1:4">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="10" t="s">
         <v>41</v>
       </c>
@@ -3929,7 +3947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:4" s="12" customFormat="1">
+    <row r="233" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A233" s="10" t="s">
         <v>41</v>
       </c>
@@ -3943,7 +3961,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="15">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="10" t="s">
         <v>42</v>
       </c>
@@ -3957,7 +3975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:4">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="10" t="s">
         <v>42</v>
       </c>
@@ -3971,7 +3989,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="236" spans="1:4">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="10" t="s">
         <v>42</v>
       </c>
@@ -3985,7 +4003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:4">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="10" t="s">
         <v>42</v>
       </c>
@@ -3999,7 +4017,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:4">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="10" t="s">
         <v>42</v>
       </c>
@@ -4013,7 +4031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:4">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" s="10" t="s">
         <v>42</v>
       </c>
@@ -4027,7 +4045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:4">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="10" t="s">
         <v>42</v>
       </c>
@@ -4041,7 +4059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="1:4" s="12" customFormat="1">
+    <row r="241" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A241" s="10" t="s">
         <v>42</v>
       </c>
@@ -4055,7 +4073,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="15">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="10" t="s">
         <v>43</v>
       </c>
@@ -4069,7 +4087,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="15">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="10" t="s">
         <v>43</v>
       </c>
@@ -4083,7 +4101,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="15">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="10" t="s">
         <v>43</v>
       </c>
@@ -4097,7 +4115,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="15">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" s="10" t="s">
         <v>43</v>
       </c>
@@ -4111,7 +4129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="15">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="10" t="s">
         <v>43</v>
       </c>
@@ -4125,7 +4143,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="15">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="10" t="s">
         <v>43</v>
       </c>
@@ -4139,7 +4157,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="15">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="10" t="s">
         <v>43</v>
       </c>
@@ -4153,7 +4171,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="15">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="14" t="s">
         <v>43</v>
       </c>
@@ -4167,7 +4185,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="15">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" s="10" t="s">
         <v>44</v>
       </c>
@@ -4181,7 +4199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="15">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" s="10" t="s">
         <v>44</v>
       </c>
@@ -4195,7 +4213,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="15">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" s="10" t="s">
         <v>44</v>
       </c>
@@ -4209,7 +4227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="15">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" s="10" t="s">
         <v>44</v>
       </c>
@@ -4223,7 +4241,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="15">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="10" t="s">
         <v>44</v>
       </c>
@@ -4237,7 +4255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="15">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="10" t="s">
         <v>44</v>
       </c>
@@ -4251,7 +4269,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="15">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" s="10" t="s">
         <v>44</v>
       </c>
@@ -4265,7 +4283,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="15">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" s="14" t="s">
         <v>44</v>
       </c>
@@ -4279,7 +4297,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="15">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="10" t="s">
         <v>45</v>
       </c>
@@ -4293,7 +4311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="15">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" s="10" t="s">
         <v>45</v>
       </c>
@@ -4307,7 +4325,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="15">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" s="10" t="s">
         <v>45</v>
       </c>
@@ -4321,7 +4339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="15">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" s="10" t="s">
         <v>45</v>
       </c>
@@ -4335,7 +4353,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="15">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" s="10" t="s">
         <v>45</v>
       </c>
@@ -4349,7 +4367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="15">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" s="10" t="s">
         <v>45</v>
       </c>
@@ -4363,7 +4381,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="15">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" s="10" t="s">
         <v>45</v>
       </c>
@@ -4377,7 +4395,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="15">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" s="14" t="s">
         <v>45</v>
       </c>
@@ -4391,7 +4409,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="15">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" s="10" t="s">
         <v>46</v>
       </c>
@@ -4405,7 +4423,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="15">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" s="10" t="s">
         <v>46</v>
       </c>
@@ -4419,7 +4437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="15">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" s="10" t="s">
         <v>46</v>
       </c>
@@ -4433,7 +4451,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="15">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" s="10" t="s">
         <v>46</v>
       </c>
@@ -4447,7 +4465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="15">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" s="10" t="s">
         <v>46</v>
       </c>
@@ -4461,7 +4479,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="271" spans="1:4" ht="15">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" s="10" t="s">
         <v>46</v>
       </c>
@@ -4475,7 +4493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:4" ht="15">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" s="10" t="s">
         <v>46</v>
       </c>
@@ -4489,7 +4507,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="15">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" s="14" t="s">
         <v>46</v>
       </c>
@@ -4503,7 +4521,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="15">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" s="10" t="s">
         <v>47</v>
       </c>
@@ -4517,7 +4535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="15">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" s="10" t="s">
         <v>47</v>
       </c>
@@ -4531,7 +4549,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="15">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" s="10" t="s">
         <v>47</v>
       </c>
@@ -4545,7 +4563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="15">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" s="10" t="s">
         <v>47</v>
       </c>
@@ -4559,7 +4577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="278" spans="1:4" ht="15">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" s="10" t="s">
         <v>47</v>
       </c>
@@ -4573,7 +4591,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="15">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" s="10" t="s">
         <v>47</v>
       </c>
@@ -4587,7 +4605,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="280" spans="1:4" ht="15">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" s="10" t="s">
         <v>47</v>
       </c>
@@ -4601,7 +4619,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="15">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" s="14" t="s">
         <v>47</v>
       </c>
@@ -4615,7 +4633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="282" spans="1:4" ht="15">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" s="10" t="s">
         <v>48</v>
       </c>
@@ -4629,7 +4647,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="283" spans="1:4" ht="15">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" s="10" t="s">
         <v>48</v>
       </c>
@@ -4643,7 +4661,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="15">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" s="10" t="s">
         <v>48</v>
       </c>
@@ -4657,7 +4675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:4" ht="15">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" s="10" t="s">
         <v>48</v>
       </c>
@@ -4671,7 +4689,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="286" spans="1:4" ht="15">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" s="10" t="s">
         <v>48</v>
       </c>
@@ -4685,7 +4703,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="15">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" s="10" t="s">
         <v>48</v>
       </c>
@@ -4699,7 +4717,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="15">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" s="10" t="s">
         <v>48</v>
       </c>
@@ -4713,7 +4731,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="15">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" s="14" t="s">
         <v>48</v>
       </c>
@@ -4727,7 +4745,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="15">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" s="10" t="s">
         <v>49</v>
       </c>
@@ -4741,7 +4759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="15">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" s="10" t="s">
         <v>49</v>
       </c>
@@ -4755,7 +4773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="15">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" s="10" t="s">
         <v>49</v>
       </c>
@@ -4769,7 +4787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="15">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" s="10" t="s">
         <v>49</v>
       </c>
@@ -4783,7 +4801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="15">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" s="10" t="s">
         <v>49</v>
       </c>
@@ -4797,7 +4815,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="15">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" s="10" t="s">
         <v>49</v>
       </c>
@@ -4811,7 +4829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="15">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" s="10" t="s">
         <v>49</v>
       </c>
@@ -4825,7 +4843,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="15">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" s="14" t="s">
         <v>49</v>
       </c>
@@ -4839,7 +4857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="15">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" s="10" t="s">
         <v>50</v>
       </c>
@@ -4853,7 +4871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="15">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" s="10" t="s">
         <v>50</v>
       </c>
@@ -4867,7 +4885,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="15">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" s="10" t="s">
         <v>50</v>
       </c>
@@ -4881,7 +4899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="15">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" s="10" t="s">
         <v>50</v>
       </c>
@@ -4895,7 +4913,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="15">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" s="10" t="s">
         <v>50</v>
       </c>
@@ -4909,7 +4927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="15">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" s="10" t="s">
         <v>50</v>
       </c>
@@ -4923,7 +4941,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="304" spans="1:4" ht="15">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" s="10" t="s">
         <v>50</v>
       </c>
@@ -4937,7 +4955,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="15">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" s="14" t="s">
         <v>50</v>
       </c>
@@ -4951,7 +4969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="15">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" s="10" t="s">
         <v>51</v>
       </c>
@@ -4965,7 +4983,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="15">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" s="10" t="s">
         <v>51</v>
       </c>
@@ -4979,7 +4997,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="15">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" s="10" t="s">
         <v>51</v>
       </c>
@@ -4993,7 +5011,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="15">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" s="10" t="s">
         <v>51</v>
       </c>
@@ -5007,7 +5025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:4" ht="15">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" s="10" t="s">
         <v>51</v>
       </c>
@@ -5021,7 +5039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:4" ht="15">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" s="10" t="s">
         <v>51</v>
       </c>
@@ -5035,7 +5053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:4" ht="15">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" s="10" t="s">
         <v>51</v>
       </c>
@@ -5049,7 +5067,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="313" spans="1:4" ht="15">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" s="14" t="s">
         <v>51</v>
       </c>
@@ -5063,7 +5081,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="314" spans="1:4" ht="15">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" s="10" t="s">
         <v>52</v>
       </c>
@@ -5077,7 +5095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" spans="1:4" ht="15">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" s="10" t="s">
         <v>52</v>
       </c>
@@ -5091,7 +5109,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="15">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" s="10" t="s">
         <v>52</v>
       </c>
@@ -5105,7 +5123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="1:4" ht="15">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" s="10" t="s">
         <v>52</v>
       </c>
@@ -5119,7 +5137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:4" ht="15">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" s="10" t="s">
         <v>52</v>
       </c>
@@ -5133,7 +5151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:4" ht="15">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" s="10" t="s">
         <v>52</v>
       </c>
@@ -5147,7 +5165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:4" ht="15">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" s="10" t="s">
         <v>52</v>
       </c>
@@ -5161,7 +5179,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="321" spans="1:4" ht="15">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" s="14" t="s">
         <v>52</v>
       </c>
@@ -5175,7 +5193,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="322" spans="1:4" ht="15">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" s="10" t="s">
         <v>53</v>
       </c>
@@ -5189,7 +5207,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:4" ht="15">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" s="10" t="s">
         <v>53</v>
       </c>
@@ -5203,7 +5221,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="324" spans="1:4" ht="15">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" s="10" t="s">
         <v>53</v>
       </c>
@@ -5217,7 +5235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:4" ht="15">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" s="10" t="s">
         <v>53</v>
       </c>
@@ -5231,7 +5249,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="326" spans="1:4" ht="15">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" s="10" t="s">
         <v>53</v>
       </c>
@@ -5245,7 +5263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="327" spans="1:4" ht="15">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" s="10" t="s">
         <v>53</v>
       </c>
@@ -5259,7 +5277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="328" spans="1:4" ht="15">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" s="10" t="s">
         <v>53</v>
       </c>
@@ -5273,7 +5291,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="329" spans="1:4" ht="15">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" s="14" t="s">
         <v>53</v>
       </c>
@@ -5287,7 +5305,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="330" spans="1:4" ht="15">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" s="10" t="s">
         <v>54</v>
       </c>
@@ -5301,7 +5319,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="15">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" s="10" t="s">
         <v>54</v>
       </c>
@@ -5315,7 +5333,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="15">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" s="10" t="s">
         <v>54</v>
       </c>
@@ -5329,7 +5347,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="15">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" s="10" t="s">
         <v>54</v>
       </c>
@@ -5343,7 +5361,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="334" spans="1:4" ht="15">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" s="10" t="s">
         <v>54</v>
       </c>
@@ -5357,7 +5375,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="335" spans="1:4" ht="15">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" s="10" t="s">
         <v>54</v>
       </c>
@@ -5371,7 +5389,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="336" spans="1:4" ht="15">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" s="10" t="s">
         <v>54</v>
       </c>
@@ -5385,7 +5403,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="337" spans="1:4" ht="15">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" s="14" t="s">
         <v>54</v>
       </c>
@@ -5399,7 +5417,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="338" spans="1:4" ht="15">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" s="10" t="s">
         <v>55</v>
       </c>
@@ -5413,7 +5431,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="15">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" s="10" t="s">
         <v>55</v>
       </c>
@@ -5427,7 +5445,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="340" spans="1:4" ht="15">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" s="10" t="s">
         <v>55</v>
       </c>
@@ -5441,7 +5459,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="341" spans="1:4" ht="15">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" s="10" t="s">
         <v>55</v>
       </c>
@@ -5455,7 +5473,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="15">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" s="10" t="s">
         <v>55</v>
       </c>
@@ -5469,7 +5487,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="343" spans="1:4" ht="15">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" s="10" t="s">
         <v>55</v>
       </c>
@@ -5483,7 +5501,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="15">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" s="10" t="s">
         <v>55</v>
       </c>
@@ -5497,7 +5515,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="345" spans="1:4" ht="15">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" s="14" t="s">
         <v>55</v>
       </c>
@@ -5511,7 +5529,7 @@
         <v>-9999</v>
       </c>
     </row>
-    <row r="346" spans="1:4" ht="15">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" s="10" t="s">
         <v>56</v>
       </c>
@@ -5525,7 +5543,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="347" spans="1:4" ht="15">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" s="10" t="s">
         <v>56</v>
       </c>
@@ -5539,7 +5557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="15">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" s="10" t="s">
         <v>56</v>
       </c>
@@ -5553,7 +5571,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="349" spans="1:4" ht="15">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349" s="10" t="s">
         <v>56</v>
       </c>
@@ -5567,7 +5585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:4" ht="15">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" s="10" t="s">
         <v>56</v>
       </c>
@@ -5581,7 +5599,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="351" spans="1:4" ht="15">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351" s="10" t="s">
         <v>56</v>
       </c>
@@ -5595,7 +5613,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="352" spans="1:4" ht="15">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" s="10" t="s">
         <v>56</v>
       </c>
@@ -5609,7 +5627,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="353" spans="1:4" ht="15">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353" s="14" t="s">
         <v>56</v>
       </c>
@@ -5623,7 +5641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="354" spans="1:4" ht="15">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" s="10" t="s">
         <v>57</v>
       </c>
@@ -5637,7 +5655,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="355" spans="1:4" ht="15">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355" s="10" t="s">
         <v>57</v>
       </c>
@@ -5651,7 +5669,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="15">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" s="10" t="s">
         <v>57</v>
       </c>
@@ -5665,7 +5683,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="15">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357" s="10" t="s">
         <v>57</v>
       </c>
@@ -5679,7 +5697,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="15">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" s="10" t="s">
         <v>57</v>
       </c>
@@ -5693,7 +5711,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="15">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" s="10" t="s">
         <v>57</v>
       </c>
@@ -5707,7 +5725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="15">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" s="10" t="s">
         <v>57</v>
       </c>
@@ -5721,7 +5739,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="361" spans="1:4" ht="15">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A361" s="14" t="s">
         <v>57</v>
       </c>
@@ -5735,14 +5753,678 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="362" spans="1:4" ht="15"/>
-    <row r="363" spans="1:4" ht="15"/>
-    <row r="364" spans="1:4" ht="15"/>
-    <row r="365" spans="1:4" ht="15"/>
-    <row r="366" spans="1:4" ht="15"/>
-    <row r="367" spans="1:4" ht="15"/>
-    <row r="368" spans="1:4" ht="15"/>
-    <row r="369" ht="15"/>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>58</v>
+      </c>
+      <c r="B362" t="s">
+        <v>5</v>
+      </c>
+      <c r="C362" t="s">
+        <v>6</v>
+      </c>
+      <c r="D362" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>58</v>
+      </c>
+      <c r="B363" t="s">
+        <v>7</v>
+      </c>
+      <c r="C363" t="s">
+        <v>6</v>
+      </c>
+      <c r="D363" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>58</v>
+      </c>
+      <c r="B364" t="s">
+        <v>5</v>
+      </c>
+      <c r="C364" t="s">
+        <v>8</v>
+      </c>
+      <c r="D364" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>58</v>
+      </c>
+      <c r="B365" t="s">
+        <v>7</v>
+      </c>
+      <c r="C365" t="s">
+        <v>8</v>
+      </c>
+      <c r="D365" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>58</v>
+      </c>
+      <c r="B366" t="s">
+        <v>5</v>
+      </c>
+      <c r="C366" t="s">
+        <v>9</v>
+      </c>
+      <c r="D366" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>58</v>
+      </c>
+      <c r="B367" t="s">
+        <v>7</v>
+      </c>
+      <c r="C367" t="s">
+        <v>9</v>
+      </c>
+      <c r="D367" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>58</v>
+      </c>
+      <c r="B368" t="s">
+        <v>5</v>
+      </c>
+      <c r="C368" t="s">
+        <v>10</v>
+      </c>
+      <c r="D368" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>58</v>
+      </c>
+      <c r="B369" t="s">
+        <v>7</v>
+      </c>
+      <c r="C369" t="s">
+        <v>10</v>
+      </c>
+      <c r="D369" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>59</v>
+      </c>
+      <c r="B370" t="s">
+        <v>5</v>
+      </c>
+      <c r="C370" t="s">
+        <v>6</v>
+      </c>
+      <c r="D370" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>59</v>
+      </c>
+      <c r="B371" t="s">
+        <v>7</v>
+      </c>
+      <c r="C371" t="s">
+        <v>6</v>
+      </c>
+      <c r="D371" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>59</v>
+      </c>
+      <c r="B372" t="s">
+        <v>5</v>
+      </c>
+      <c r="C372" t="s">
+        <v>8</v>
+      </c>
+      <c r="D372" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>59</v>
+      </c>
+      <c r="B373" t="s">
+        <v>7</v>
+      </c>
+      <c r="C373" t="s">
+        <v>8</v>
+      </c>
+      <c r="D373" s="6">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>59</v>
+      </c>
+      <c r="B374" t="s">
+        <v>5</v>
+      </c>
+      <c r="C374" t="s">
+        <v>9</v>
+      </c>
+      <c r="D374" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>59</v>
+      </c>
+      <c r="B375" t="s">
+        <v>7</v>
+      </c>
+      <c r="C375" t="s">
+        <v>9</v>
+      </c>
+      <c r="D375" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>59</v>
+      </c>
+      <c r="B376" t="s">
+        <v>5</v>
+      </c>
+      <c r="C376" t="s">
+        <v>10</v>
+      </c>
+      <c r="D376" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>59</v>
+      </c>
+      <c r="B377" t="s">
+        <v>7</v>
+      </c>
+      <c r="C377" t="s">
+        <v>10</v>
+      </c>
+      <c r="D377" s="6">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>60</v>
+      </c>
+      <c r="B378" t="s">
+        <v>5</v>
+      </c>
+      <c r="C378" t="s">
+        <v>6</v>
+      </c>
+      <c r="D378" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>60</v>
+      </c>
+      <c r="B379" t="s">
+        <v>7</v>
+      </c>
+      <c r="C379" t="s">
+        <v>6</v>
+      </c>
+      <c r="D379" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>60</v>
+      </c>
+      <c r="B380" t="s">
+        <v>5</v>
+      </c>
+      <c r="C380" t="s">
+        <v>8</v>
+      </c>
+      <c r="D380" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>60</v>
+      </c>
+      <c r="B381" t="s">
+        <v>7</v>
+      </c>
+      <c r="C381" t="s">
+        <v>8</v>
+      </c>
+      <c r="D381" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>60</v>
+      </c>
+      <c r="B382" t="s">
+        <v>5</v>
+      </c>
+      <c r="C382" t="s">
+        <v>9</v>
+      </c>
+      <c r="D382" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>60</v>
+      </c>
+      <c r="B383" t="s">
+        <v>7</v>
+      </c>
+      <c r="C383" t="s">
+        <v>9</v>
+      </c>
+      <c r="D383" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>60</v>
+      </c>
+      <c r="B384" t="s">
+        <v>5</v>
+      </c>
+      <c r="C384" t="s">
+        <v>10</v>
+      </c>
+      <c r="D384" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>60</v>
+      </c>
+      <c r="B385" t="s">
+        <v>7</v>
+      </c>
+      <c r="C385" t="s">
+        <v>10</v>
+      </c>
+      <c r="D385" s="6">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>61</v>
+      </c>
+      <c r="B386" t="s">
+        <v>5</v>
+      </c>
+      <c r="C386" t="s">
+        <v>6</v>
+      </c>
+      <c r="D386" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>61</v>
+      </c>
+      <c r="B387" t="s">
+        <v>7</v>
+      </c>
+      <c r="C387" t="s">
+        <v>6</v>
+      </c>
+      <c r="D387" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>61</v>
+      </c>
+      <c r="B388" t="s">
+        <v>5</v>
+      </c>
+      <c r="C388" t="s">
+        <v>8</v>
+      </c>
+      <c r="D388" s="6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>61</v>
+      </c>
+      <c r="B389" t="s">
+        <v>7</v>
+      </c>
+      <c r="C389" t="s">
+        <v>8</v>
+      </c>
+      <c r="D389" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>61</v>
+      </c>
+      <c r="B390" t="s">
+        <v>5</v>
+      </c>
+      <c r="C390" t="s">
+        <v>9</v>
+      </c>
+      <c r="D390" s="6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>61</v>
+      </c>
+      <c r="B391" t="s">
+        <v>7</v>
+      </c>
+      <c r="C391" t="s">
+        <v>9</v>
+      </c>
+      <c r="D391" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>61</v>
+      </c>
+      <c r="B392" t="s">
+        <v>5</v>
+      </c>
+      <c r="C392" t="s">
+        <v>10</v>
+      </c>
+      <c r="D392" s="6">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>61</v>
+      </c>
+      <c r="B393" t="s">
+        <v>7</v>
+      </c>
+      <c r="C393" t="s">
+        <v>10</v>
+      </c>
+      <c r="D393" s="6">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>62</v>
+      </c>
+      <c r="B394" t="s">
+        <v>5</v>
+      </c>
+      <c r="C394" t="s">
+        <v>6</v>
+      </c>
+      <c r="D394" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>62</v>
+      </c>
+      <c r="B395" t="s">
+        <v>7</v>
+      </c>
+      <c r="C395" t="s">
+        <v>6</v>
+      </c>
+      <c r="D395" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>62</v>
+      </c>
+      <c r="B396" t="s">
+        <v>5</v>
+      </c>
+      <c r="C396" t="s">
+        <v>8</v>
+      </c>
+      <c r="D396" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>62</v>
+      </c>
+      <c r="B397" t="s">
+        <v>7</v>
+      </c>
+      <c r="C397" t="s">
+        <v>8</v>
+      </c>
+      <c r="D397" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>62</v>
+      </c>
+      <c r="B398" t="s">
+        <v>5</v>
+      </c>
+      <c r="C398" t="s">
+        <v>9</v>
+      </c>
+      <c r="D398" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>62</v>
+      </c>
+      <c r="B399" t="s">
+        <v>7</v>
+      </c>
+      <c r="C399" t="s">
+        <v>9</v>
+      </c>
+      <c r="D399" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>62</v>
+      </c>
+      <c r="B400" t="s">
+        <v>5</v>
+      </c>
+      <c r="C400" t="s">
+        <v>10</v>
+      </c>
+      <c r="D400" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>62</v>
+      </c>
+      <c r="B401" t="s">
+        <v>7</v>
+      </c>
+      <c r="C401" t="s">
+        <v>10</v>
+      </c>
+      <c r="D401" s="6">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>63</v>
+      </c>
+      <c r="B402" t="s">
+        <v>5</v>
+      </c>
+      <c r="C402" t="s">
+        <v>6</v>
+      </c>
+      <c r="D402" s="6">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>63</v>
+      </c>
+      <c r="B403" t="s">
+        <v>7</v>
+      </c>
+      <c r="C403" t="s">
+        <v>6</v>
+      </c>
+      <c r="D403" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>63</v>
+      </c>
+      <c r="B404" t="s">
+        <v>5</v>
+      </c>
+      <c r="C404" t="s">
+        <v>8</v>
+      </c>
+      <c r="D404" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>63</v>
+      </c>
+      <c r="B405" t="s">
+        <v>7</v>
+      </c>
+      <c r="C405" t="s">
+        <v>8</v>
+      </c>
+      <c r="D405" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>63</v>
+      </c>
+      <c r="B406" t="s">
+        <v>5</v>
+      </c>
+      <c r="C406" t="s">
+        <v>9</v>
+      </c>
+      <c r="D406" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>63</v>
+      </c>
+      <c r="B407" t="s">
+        <v>7</v>
+      </c>
+      <c r="C407" t="s">
+        <v>9</v>
+      </c>
+      <c r="D407" s="6">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>63</v>
+      </c>
+      <c r="B408" t="s">
+        <v>5</v>
+      </c>
+      <c r="C408" t="s">
+        <v>10</v>
+      </c>
+      <c r="D408" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>63</v>
+      </c>
+      <c r="B409" t="s">
+        <v>7</v>
+      </c>
+      <c r="C409" t="s">
+        <v>10</v>
+      </c>
+      <c r="D409" s="6">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5759,6 +6441,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71842362-ab5d-46b4-b35f-08dc9c6328ce">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8def90a7-5747-4395-b698-a599996d7912" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006131D81E7FE36E44885B3A04523FCF5D" ma:contentTypeVersion="14" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8f9efaeda295997044994eea58453835">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71842362-ab5d-46b4-b35f-08dc9c6328ce" xmlns:ns3="8def90a7-5747-4395-b698-a599996d7912" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7a2e7ed8b28d563a97a27396956f6ac0" ns2:_="" ns3:_="">
     <xsd:import namespace="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
@@ -5987,25 +6680,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71842362-ab5d-46b4-b35f-08dc9c6328ce">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8def90a7-5747-4395-b698-a599996d7912" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11C6C99-7A10-4A95-96FC-EB882D282983}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B11C6C99-7A10-4A95-96FC-EB882D282983}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79464CFF-4EB4-4262-9D1E-A0E9F07A9D35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{380DF39A-B0F0-4341-AFC9-AAFA55711E66}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
+    <ds:schemaRef ds:uri="8def90a7-5747-4395-b698-a599996d7912"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{380DF39A-B0F0-4341-AFC9-AAFA55711E66}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79464CFF-4EB4-4262-9D1E-A0E9F07A9D35}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="71842362-ab5d-46b4-b35f-08dc9c6328ce"/>
+    <ds:schemaRef ds:uri="8def90a7-5747-4395-b698-a599996d7912"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>